--- a/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO-Agent运行结果-20260925-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO-Agent运行结果-20260925-V1.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent总览" sheetId="1" r:id="R3d741d5bcdbb4a71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="管理层摘要" sheetId="2" r:id="Ra1cfa8c2dde94410"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发现清单" sheetId="3" r:id="Rc094e2c948024918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据明细" sheetId="4" r:id="R8103b209f7054f7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="5" r:id="R2a7de67db2064156"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent总览" sheetId="1" r:id="R80eff0f994de4db1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="管理层摘要" sheetId="2" r:id="Rbc8f1a6b8b0e4556"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发现清单" sheetId="3" r:id="Rec5a27c2985e4634"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据明细" sheetId="4" r:id="R733357303ca44843"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="5" r:id="R0feaf4768aaa47ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -429,7 +429,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
-        <x:v>数据日期 2026-09-25｜运行ID AGENT-20260925-082601</x:v>
+        <x:v>数据日期 2026-09-25｜运行ID AGENT-20260925-085337</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
@@ -473,11 +473,11 @@
       </x:c>
       <x:c r="D6" s="12" t="n">
         <x:f>COUNTIF('发现清单'!$C$5:$C$204,"高")</x:f>
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
         <x:f>COUNTIF('发现清单'!$C$5:$C$204,"中")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="12" t="n">
         <x:f>COUNTIF('发现清单'!$I$5:$I$204,"是")</x:f>
@@ -656,10 +656,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="D6" s="12" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="12" t="n">
         <x:v>29</x:v>
@@ -687,13 +687,13 @@
         <x:v>重大</x:v>
       </x:c>
       <x:c r="B10" s="18" t="str">
-        <x:v>待决策事项</x:v>
+        <x:v>决策事项7天内到期</x:v>
       </x:c>
       <x:c r="C10" s="18" t="str">
         <x:v>D-001</x:v>
       </x:c>
       <x:c r="D10" s="18" t="str">
-        <x:v>单一入围；分产品入围；补充POC</x:v>
+        <x:v>项目指导委员会</x:v>
       </x:c>
       <x:c r="E10" s="18" t="str">
         <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
@@ -710,7 +710,7 @@
         <x:v>D-002</x:v>
       </x:c>
       <x:c r="D11" s="18" t="str">
-        <x:v>一次性全量；P0优先分阶段</x:v>
+        <x:v>业务负责人/项目发起人</x:v>
       </x:c>
       <x:c r="E11" s="18" t="str">
         <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
@@ -727,7 +727,7 @@
         <x:v>D-003</x:v>
       </x:c>
       <x:c r="D12" s="18" t="str">
-        <x:v>统一采购；分项采购；框架协议</x:v>
+        <x:v>项目发起人</x:v>
       </x:c>
       <x:c r="E12" s="18" t="str">
         <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
@@ -744,7 +744,7 @@
         <x:v>D-004</x:v>
       </x:c>
       <x:c r="D13" s="18" t="str">
-        <x:v>通过；有条件通过；不通过</x:v>
+        <x:v>项目指导委员会</x:v>
       </x:c>
       <x:c r="E13" s="18" t="str">
         <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
@@ -880,7 +880,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F5" s="18" t="str">
-        <x:v>【连续第3期出现】汇编可研报告并组织评审计划完成日为2026-09-18，当前状态为进行中。</x:v>
+        <x:v>【连续第4期出现】汇编可研报告并组织评审计划完成日为2026-09-18，当前状态为进行中。</x:v>
       </x:c>
       <x:c r="G5" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -895,7 +895,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K5" s="10" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L5" s="10" t="str"/>
       <x:c r="M5" s="21" t="str">
@@ -920,7 +920,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F6" s="18" t="str">
-        <x:v>【连续第9期出现】盘点既有系统、接口与数据计划完成日为2026-05-05，当前状态为进行中。</x:v>
+        <x:v>【连续第10期出现】盘点既有系统、接口与数据计划完成日为2026-05-05，当前状态为进行中。</x:v>
       </x:c>
       <x:c r="G6" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -935,7 +935,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K6" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L6" s="10" t="str"/>
       <x:c r="M6" s="21" t="str">
@@ -960,7 +960,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F7" s="18" t="str">
-        <x:v>【连续第9期出现】访谈业务部门并形成痛点清单计划完成日为2026-06-02，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】访谈业务部门并形成痛点清单计划完成日为2026-06-02，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G7" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -975,7 +975,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K7" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L7" s="10" t="str"/>
       <x:c r="M7" s="21" t="str">
@@ -1000,7 +1000,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F8" s="18" t="str">
-        <x:v>【连续第9期出现】确认现状流程、问题与改进机会基线计划完成日为2026-06-30，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】确认现状流程、问题与改进机会基线计划完成日为2026-06-30，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G8" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1015,7 +1015,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K8" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L8" s="10" t="str"/>
       <x:c r="M8" s="21" t="str">
@@ -1040,7 +1040,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F9" s="18" t="str">
-        <x:v>【连续第9期出现】制定项目治理、会议与报告机制计划完成日为2026-07-12，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】制定项目治理、会议与报告机制计划完成日为2026-07-12，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G9" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1055,7 +1055,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K9" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L9" s="10" t="str"/>
       <x:c r="M9" s="21" t="str">
@@ -1080,7 +1080,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F10" s="18" t="str">
-        <x:v>【连续第9期出现】制定需求分级、跟踪与变更规范计划完成日为2026-07-24，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】制定需求分级、跟踪与变更规范计划完成日为2026-07-24，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G10" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1095,7 +1095,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K10" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L10" s="10" t="str"/>
       <x:c r="M10" s="21" t="str">
@@ -1120,7 +1120,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F11" s="18" t="str">
-        <x:v>【连续第9期出现】制定设计、编码与代码评审规范计划完成日为2026-08-06，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】制定设计、编码与代码评审规范计划完成日为2026-08-06，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G11" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1135,7 +1135,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K11" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L11" s="10" t="str"/>
       <x:c r="M11" s="21" t="str">
@@ -1160,7 +1160,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F12" s="18" t="str">
-        <x:v>【连续第9期出现】制定测试、缺陷与质量门禁规范计划完成日为2026-08-18，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】制定测试、缺陷与质量门禁规范计划完成日为2026-08-18，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G12" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1175,7 +1175,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K12" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L12" s="10" t="str"/>
       <x:c r="M12" s="21" t="str">
@@ -1200,7 +1200,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F13" s="18" t="str">
-        <x:v>【连续第9期出现】制定配置、发布与文档归档规范计划完成日为2026-08-31，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】制定配置、发布与文档归档规范计划完成日为2026-08-31，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G13" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1215,7 +1215,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K13" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L13" s="10" t="str"/>
       <x:c r="M13" s="21" t="str">
@@ -1240,7 +1240,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F14" s="18" t="str">
-        <x:v>【连续第9期出现】完成系统分层、模块与服务边界设计计划完成日为2026-07-15，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】完成系统分层、模块与服务边界设计计划完成日为2026-07-15，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G14" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1255,7 +1255,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K14" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L14" s="10" t="str"/>
       <x:c r="M14" s="21" t="str">
@@ -1280,7 +1280,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F15" s="18" t="str">
-        <x:v>【连续第9期出现】完成主数据、交易数据与分析数据架构计划完成日为2026-07-30，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】完成主数据、交易数据与分析数据架构计划完成日为2026-07-30，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G15" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1295,7 +1295,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K15" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L15" s="10" t="str"/>
       <x:c r="M15" s="21" t="str">
@@ -1320,7 +1320,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F16" s="18" t="str">
-        <x:v>【连续第9期出现】完成内部及外部接口总体架构计划完成日为2026-08-15，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】完成内部及外部接口总体架构计划完成日为2026-08-15，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G16" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1335,7 +1335,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K16" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L16" s="10" t="str"/>
       <x:c r="M16" s="21" t="str">
@@ -1360,7 +1360,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F17" s="18" t="str">
-        <x:v>【连续第9期出现】完成身份、权限、审计与数据安全设计计划完成日为2026-08-30，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】完成身份、权限、审计与数据安全设计计划完成日为2026-08-30，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G17" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1375,7 +1375,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K17" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L17" s="10" t="str"/>
       <x:c r="M17" s="21" t="str">
@@ -1400,7 +1400,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F18" s="18" t="str">
-        <x:v>【连续第9期出现】完成环境、网络、容灾和DevOps设计计划完成日为2026-09-14，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】完成环境、网络、容灾和DevOps设计计划完成日为2026-09-14，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G18" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1415,7 +1415,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K18" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L18" s="10" t="str"/>
       <x:c r="M18" s="21" t="str">
@@ -1440,7 +1440,7 @@
         <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F19" s="18" t="str">
-        <x:v>【连续第9期出现】汇编总体技术架构并完成基线评审将在2026-09-30到期，当前状态为进行中。</x:v>
+        <x:v>【连续第10期出现】汇编总体技术架构并完成基线评审将在2026-09-30到期，当前状态为进行中。</x:v>
       </x:c>
       <x:c r="G19" s="18" t="str">
         <x:v>确认交付物、验收人和按期完成证据。</x:v>
@@ -1455,7 +1455,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K19" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L19" s="10" t="str"/>
       <x:c r="M19" s="21" t="str">
@@ -1480,7 +1480,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F20" s="18" t="str">
-        <x:v>【连续第9期出现】编制CA、电子文档、BI报表POC方案与评分标准计划完成日为2026-08-19，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】编制CA、电子文档、BI报表POC方案与评分标准计划完成日为2026-08-19，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G20" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1495,7 +1495,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K20" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L20" s="10" t="str"/>
       <x:c r="M20" s="21" t="str">
@@ -1520,7 +1520,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F21" s="18" t="str">
-        <x:v>【连续第9期出现】验证证书签发、身份认证和证书管理计划完成日为2026-08-24，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】验证证书签发、身份认证和证书管理计划完成日为2026-08-24，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G21" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1535,7 +1535,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K21" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L21" s="10" t="str"/>
       <x:c r="M21" s="21" t="str">
@@ -1560,7 +1560,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F22" s="18" t="str">
-        <x:v>【连续第9期出现】验证电子签名、验签、时间戳和审计追溯计划完成日为2026-08-29，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】验证电子签名、验签、时间戳和审计追溯计划完成日为2026-08-29，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G22" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1575,7 +1575,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K22" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L22" s="10" t="str"/>
       <x:c r="M22" s="21" t="str">
@@ -1600,7 +1600,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F23" s="18" t="str">
-        <x:v>【连续第9期出现】验证模板生成、在线预览和格式转换计划完成日为2026-09-04，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】验证模板生成、在线预览和格式转换计划完成日为2026-09-04，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G23" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1615,7 +1615,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K23" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L23" s="10" t="str"/>
       <x:c r="M23" s="21" t="str">
@@ -1640,7 +1640,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F24" s="18" t="str">
-        <x:v>【连续第9期出现】验证水印、权限控制、归档和大文件性能计划完成日为2026-09-09，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】验证水印、权限控制、归档和大文件性能计划完成日为2026-09-09，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G24" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1655,7 +1655,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K24" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L24" s="10" t="str"/>
       <x:c r="M24" s="21" t="str">
@@ -1680,7 +1680,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F25" s="18" t="str">
-        <x:v>【连续第9期出现】验证数据接入、指标模型和经营报表计划完成日为2026-09-14，当前状态为待确认。</x:v>
+        <x:v>【连续第10期出现】验证数据接入、指标模型和经营报表计划完成日为2026-09-14，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G25" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1695,7 +1695,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K25" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L25" s="10" t="str"/>
       <x:c r="M25" s="21" t="str">
@@ -1720,7 +1720,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F26" s="18" t="str">
-        <x:v>【连续第3期出现】验证权限、钻取、导出和查询性能计划完成日为2026-09-19，当前状态为进行中。</x:v>
+        <x:v>【连续第4期出现】验证权限、钻取、导出和查询性能计划完成日为2026-09-19，当前状态为进行中。</x:v>
       </x:c>
       <x:c r="G26" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1735,7 +1735,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K26" s="10" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L26" s="10" t="str"/>
       <x:c r="M26" s="21" t="str">
@@ -1760,7 +1760,7 @@
         <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F27" s="18" t="str">
-        <x:v>【连续第9期出现】汇总问题清单、适配结论和产品选型建议将在2026-09-25到期，当前状态为未开始。</x:v>
+        <x:v>【连续第10期出现】汇总问题清单、适配结论和产品选型建议将在2026-09-25到期，当前状态为未开始。</x:v>
       </x:c>
       <x:c r="G27" s="18" t="str">
         <x:v>确认交付物、验收人和按期完成证据。</x:v>
@@ -1775,7 +1775,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K27" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L27" s="10" t="str"/>
       <x:c r="M27" s="21" t="str">
@@ -1800,7 +1800,7 @@
         <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F28" s="18" t="str">
-        <x:v>【连续第9期出现】编制并审批项目章程将在2026-10-02到期，当前状态为未开始。</x:v>
+        <x:v>【连续第10期出现】编制并审批项目章程将在2026-10-02到期，当前状态为未开始。</x:v>
       </x:c>
       <x:c r="G28" s="18" t="str">
         <x:v>确认交付物、验收人和按期完成证据。</x:v>
@@ -1815,7 +1815,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K28" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L28" s="10" t="str"/>
       <x:c r="M28" s="21" t="str">
@@ -1840,7 +1840,7 @@
         <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F29" s="18" t="str">
-        <x:v>【连续第3期出现】编制范围、里程碑和主进度计划将在2026-10-05到期，当前状态为未开始。</x:v>
+        <x:v>【连续第4期出现】编制范围、里程碑和主进度计划将在2026-10-05到期，当前状态为未开始。</x:v>
       </x:c>
       <x:c r="G29" s="18" t="str">
         <x:v>确认交付物、验收人和按期完成证据。</x:v>
@@ -1855,7 +1855,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K29" s="10" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L29" s="10" t="str"/>
       <x:c r="M29" s="21" t="str">
@@ -1870,8 +1870,8 @@
       <x:c r="B30" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C30" s="21" t="str">
-        <x:v>中</x:v>
+      <x:c r="C30" s="23" t="str">
+        <x:v>高</x:v>
       </x:c>
       <x:c r="D30" s="10" t="str">
         <x:v>T035</x:v>
@@ -1880,7 +1880,7 @@
         <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F30" s="18" t="str">
-        <x:v>【连续第2期出现】建立项目组织、RACI与沟通机制将在2026-10-08到期，当前状态为未开始。</x:v>
+        <x:v>【连续第3期出现】建立项目组织、RACI与沟通机制将在2026-10-08到期，当前状态为未开始。</x:v>
       </x:c>
       <x:c r="G30" s="18" t="str">
         <x:v>确认交付物、验收人和按期完成证据。</x:v>
@@ -1895,7 +1895,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K30" s="10" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L30" s="10" t="str"/>
       <x:c r="M30" s="21" t="str">
@@ -1920,7 +1920,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F31" s="18" t="str">
-        <x:v>【连续第9期出现】CA、电子文档、BI产品POC与选型未按期完成</x:v>
+        <x:v>【连续第10期出现】CA、电子文档、BI产品POC与选型未按期完成</x:v>
       </x:c>
       <x:c r="G31" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -1935,7 +1935,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K31" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L31" s="10" t="str"/>
       <x:c r="M31" s="21" t="str">
@@ -1960,7 +1960,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F32" s="18" t="str">
-        <x:v>【连续第9期出现】总体技术架构基线未通过评审</x:v>
+        <x:v>【连续第10期出现】总体技术架构基线未通过评审</x:v>
       </x:c>
       <x:c r="G32" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -1975,7 +1975,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K32" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L32" s="10" t="str"/>
       <x:c r="M32" s="21" t="str">
@@ -2000,7 +2000,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F33" s="18" t="str">
-        <x:v>【连续第9期出现】外部系统接口边界与联调窗口不明确</x:v>
+        <x:v>【连续第10期出现】外部系统接口边界与联调窗口不明确</x:v>
       </x:c>
       <x:c r="G33" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -2015,7 +2015,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K33" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L33" s="10" t="str"/>
       <x:c r="M33" s="21" t="str">
@@ -2040,7 +2040,7 @@
         <x:v>重大剩余风险</x:v>
       </x:c>
       <x:c r="F34" s="18" t="str">
-        <x:v>【连续第9期出现】安全合规基线未形成或外部产品不满足要求</x:v>
+        <x:v>【连续第10期出现】安全合规基线未形成或外部产品不满足要求</x:v>
       </x:c>
       <x:c r="G34" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -2055,7 +2055,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K34" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L34" s="10" t="str"/>
       <x:c r="M34" s="21" t="str">
@@ -2080,7 +2080,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F35" s="18" t="str">
-        <x:v>【连续第9期出现】30人团队未按阶段计划到位</x:v>
+        <x:v>【连续第10期出现】30人团队未按阶段计划到位</x:v>
       </x:c>
       <x:c r="G35" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -2095,7 +2095,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K35" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L35" s="10" t="str"/>
       <x:c r="M35" s="21" t="str">
@@ -2120,7 +2120,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F36" s="18" t="str">
-        <x:v>【连续第9期出现】一期范围与需求基线未确认</x:v>
+        <x:v>【连续第10期出现】一期范围与需求基线未确认</x:v>
       </x:c>
       <x:c r="G36" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -2135,7 +2135,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K36" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L36" s="10" t="str"/>
       <x:c r="M36" s="21" t="str">
@@ -2160,7 +2160,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F37" s="18" t="str">
-        <x:v>【连续第9期出现】历史合同数据质量不足或迁移范围失控</x:v>
+        <x:v>【连续第10期出现】历史合同数据质量不足或迁移范围失控</x:v>
       </x:c>
       <x:c r="G37" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -2175,7 +2175,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K37" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L37" s="10" t="str"/>
       <x:c r="M37" s="21" t="str">
@@ -2200,7 +2200,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F38" s="18" t="str">
-        <x:v>【连续第9期出现】外部产品采购与合同条款不能支撑项目计划</x:v>
+        <x:v>【连续第10期出现】外部产品采购与合同条款不能支撑项目计划</x:v>
       </x:c>
       <x:c r="G38" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -2215,7 +2215,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K38" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L38" s="10" t="str"/>
       <x:c r="M38" s="21" t="str">
@@ -2240,7 +2240,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F39" s="18" t="str">
-        <x:v>【连续第9期出现】项目章程和整体管理计划未正式批准</x:v>
+        <x:v>【连续第10期出现】项目章程和整体管理计划未正式批准</x:v>
       </x:c>
       <x:c r="G39" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -2255,7 +2255,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K39" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L39" s="10" t="str"/>
       <x:c r="M39" s="21" t="str">
@@ -2280,7 +2280,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F40" s="18" t="str">
-        <x:v>【连续第9期出现】CA、电子文档、BI产品POC与选型未按期完成：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第10期出现】CA、电子文档、BI产品POC与选型未按期完成：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G40" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -2295,7 +2295,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K40" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L40" s="10" t="str"/>
       <x:c r="M40" s="21" t="str">
@@ -2320,7 +2320,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F41" s="18" t="str">
-        <x:v>【连续第9期出现】总体技术架构基线未通过评审：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第10期出现】总体技术架构基线未通过评审：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G41" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -2335,7 +2335,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K41" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L41" s="10" t="str"/>
       <x:c r="M41" s="21" t="str">
@@ -2360,7 +2360,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F42" s="18" t="str">
-        <x:v>【连续第9期出现】外部系统接口边界与联调窗口不明确：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第10期出现】外部系统接口边界与联调窗口不明确：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G42" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -2375,7 +2375,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K42" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L42" s="10" t="str"/>
       <x:c r="M42" s="21" t="str">
@@ -2400,7 +2400,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F43" s="18" t="str">
-        <x:v>【连续第9期出现】安全合规基线未形成或外部产品不满足要求：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第10期出现】安全合规基线未形成或外部产品不满足要求：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G43" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -2415,7 +2415,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K43" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L43" s="10" t="str"/>
       <x:c r="M43" s="21" t="str">
@@ -2440,7 +2440,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F44" s="18" t="str">
-        <x:v>【连续第9期出现】30人团队未按阶段计划到位：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第10期出现】30人团队未按阶段计划到位：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G44" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -2455,7 +2455,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K44" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L44" s="10" t="str"/>
       <x:c r="M44" s="21" t="str">
@@ -2480,7 +2480,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F45" s="18" t="str">
-        <x:v>【连续第9期出现】一期范围与需求基线未确认：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第10期出现】一期范围与需求基线未确认：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G45" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -2495,7 +2495,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K45" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L45" s="10" t="str"/>
       <x:c r="M45" s="21" t="str">
@@ -2520,7 +2520,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F46" s="18" t="str">
-        <x:v>【连续第9期出现】历史合同数据质量不足或迁移范围失控：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第10期出现】历史合同数据质量不足或迁移范围失控：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G46" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -2535,7 +2535,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K46" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L46" s="10" t="str"/>
       <x:c r="M46" s="21" t="str">
@@ -2560,7 +2560,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F47" s="18" t="str">
-        <x:v>【连续第9期出现】外部产品采购与合同条款不能支撑项目计划：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第10期出现】外部产品采购与合同条款不能支撑项目计划：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G47" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -2575,7 +2575,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K47" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L47" s="10" t="str"/>
       <x:c r="M47" s="21" t="str">
@@ -2600,7 +2600,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F48" s="18" t="str">
-        <x:v>【连续第9期出现】项目章程和整体管理计划未正式批准：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第10期出现】项目章程和整体管理计划未正式批准：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G48" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -2615,7 +2615,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K48" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L48" s="10" t="str"/>
       <x:c r="M48" s="21" t="str">
@@ -2640,7 +2640,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F49" s="18" t="str">
-        <x:v>【连续第9期出现】开发测试环境和配置管理未就绪：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第10期出现】开发测试环境和配置管理未就绪：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G49" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -2655,7 +2655,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K49" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L49" s="10" t="str"/>
       <x:c r="M49" s="21" t="str">
@@ -2680,7 +2680,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F50" s="18" t="str">
-        <x:v>【连续第9期出现】预算与成本控制口径未批准：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第10期出现】预算与成本控制口径未批准：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G50" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -2695,7 +2695,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K50" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L50" s="10" t="str"/>
       <x:c r="M50" s="21" t="str">
@@ -2720,7 +2720,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F51" s="18" t="str">
-        <x:v>【连续第9期出现】关键相关方对目标、范围和职责认知不一致：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第10期出现】关键相关方对目标、范围和职责认知不一致：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G51" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -2735,7 +2735,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K51" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L51" s="10" t="str"/>
       <x:c r="M51" s="21" t="str">
@@ -2757,16 +2757,16 @@
         <x:v>D-001</x:v>
       </x:c>
       <x:c r="E52" s="10" t="str">
-        <x:v>待决策事项</x:v>
+        <x:v>决策事项7天内到期</x:v>
       </x:c>
       <x:c r="F52" s="18" t="str">
-        <x:v>【连续第9期出现】2026-09-16 00:00:00</x:v>
+        <x:v>【连续第10期出现】CA、电子文档、BI产品选型（需要日期2026-09-25）</x:v>
       </x:c>
       <x:c r="G52" s="18" t="str">
         <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
       </x:c>
       <x:c r="H52" s="10" t="str">
-        <x:v>单一入围；分产品入围；补充POC</x:v>
+        <x:v>项目指导委员会</x:v>
       </x:c>
       <x:c r="I52" s="10" t="str">
         <x:v>是</x:v>
@@ -2775,7 +2775,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K52" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L52" s="10" t="str"/>
       <x:c r="M52" s="21" t="str">
@@ -2800,13 +2800,13 @@
         <x:v>待决策事项</x:v>
       </x:c>
       <x:c r="F53" s="18" t="str">
-        <x:v>【连续第9期出现】2026-09-16 00:00:00</x:v>
+        <x:v>【连续第10期出现】一期范围与P0需求基线（需要日期2026-10-09）</x:v>
       </x:c>
       <x:c r="G53" s="18" t="str">
         <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
       </x:c>
       <x:c r="H53" s="10" t="str">
-        <x:v>一次性全量；P0优先分阶段</x:v>
+        <x:v>业务负责人/项目发起人</x:v>
       </x:c>
       <x:c r="I53" s="10" t="str">
         <x:v>是</x:v>
@@ -2815,7 +2815,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K53" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L53" s="10" t="str"/>
       <x:c r="M53" s="21" t="str">
@@ -2840,13 +2840,13 @@
         <x:v>待决策事项</x:v>
       </x:c>
       <x:c r="F54" s="18" t="str">
-        <x:v>【连续第9期出现】2026-09-16 00:00:00</x:v>
+        <x:v>【连续第10期出现】项目预算与采购路径（需要日期2026-10-08）</x:v>
       </x:c>
       <x:c r="G54" s="18" t="str">
         <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
       </x:c>
       <x:c r="H54" s="10" t="str">
-        <x:v>统一采购；分项采购；框架协议</x:v>
+        <x:v>项目发起人</x:v>
       </x:c>
       <x:c r="I54" s="10" t="str">
         <x:v>是</x:v>
@@ -2855,7 +2855,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K54" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L54" s="10" t="str"/>
       <x:c r="M54" s="21" t="str">
@@ -2880,13 +2880,13 @@
         <x:v>待决策事项</x:v>
       </x:c>
       <x:c r="F55" s="18" t="str">
-        <x:v>【连续第9期出现】2026-09-16 00:00:00</x:v>
+        <x:v>【连续第10期出现】2026年10月20日正式启动决策（需要日期2026-10-16）</x:v>
       </x:c>
       <x:c r="G55" s="18" t="str">
         <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
       </x:c>
       <x:c r="H55" s="10" t="str">
-        <x:v>通过；有条件通过；不通过</x:v>
+        <x:v>项目指导委员会</x:v>
       </x:c>
       <x:c r="I55" s="10" t="str">
         <x:v>是</x:v>
@@ -2895,7 +2895,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K55" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L55" s="10" t="str"/>
       <x:c r="M55" s="21" t="str">
@@ -2920,7 +2920,7 @@
         <x:v>决策事项14天内到期</x:v>
       </x:c>
       <x:c r="F56" s="18" t="str">
-        <x:v>【连续第4期出现】CA产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
+        <x:v>【连续第5期出现】CA产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
       </x:c>
       <x:c r="G56" s="18" t="str">
         <x:v>将事实、备选方案、影响、建议和所需授权统一提交决策人。</x:v>
@@ -2935,7 +2935,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K56" s="10" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L56" s="10" t="str"/>
       <x:c r="M56" s="21" t="str">
@@ -2960,7 +2960,7 @@
         <x:v>决策事项14天内到期</x:v>
       </x:c>
       <x:c r="F57" s="18" t="str">
-        <x:v>【连续第4期出现】电子文档产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
+        <x:v>【连续第5期出现】电子文档产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
       </x:c>
       <x:c r="G57" s="18" t="str">
         <x:v>将事实、备选方案、影响、建议和所需授权统一提交决策人。</x:v>
@@ -2975,7 +2975,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K57" s="10" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L57" s="10" t="str"/>
       <x:c r="M57" s="21" t="str">
@@ -3000,7 +3000,7 @@
         <x:v>决策事项14天内到期</x:v>
       </x:c>
       <x:c r="F58" s="18" t="str">
-        <x:v>【连续第4期出现】BI报表产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
+        <x:v>【连续第5期出现】BI报表产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
       </x:c>
       <x:c r="G58" s="18" t="str">
         <x:v>将事实、备选方案、影响、建议和所需授权统一提交决策人。</x:v>
@@ -3015,7 +3015,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K58" s="10" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L58" s="10" t="str"/>
       <x:c r="M58" s="21" t="str">
@@ -4044,7 +4044,7 @@
         <x:v>运行ID</x:v>
       </x:c>
       <x:c r="B7" s="18" t="str">
-        <x:v>AGENT-20260925-082601</x:v>
+        <x:v>AGENT-20260925-085337</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">

--- a/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO-Agent运行结果-20260925-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO-Agent运行结果-20260925-V1.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent总览" sheetId="1" r:id="R80eff0f994de4db1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="管理层摘要" sheetId="2" r:id="Rbc8f1a6b8b0e4556"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发现清单" sheetId="3" r:id="Rec5a27c2985e4634"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据明细" sheetId="4" r:id="R733357303ca44843"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="5" r:id="R0feaf4768aaa47ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent总览" sheetId="1" r:id="R365e2b64bb3b4ba2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="管理层摘要" sheetId="2" r:id="R287972e717ab42b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发现清单" sheetId="3" r:id="Rdf58ee14b71c4ef8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据明细" sheetId="4" r:id="R0dd27842189a45d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="5" r:id="R058ff9b194ca42f1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -429,7 +429,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
-        <x:v>数据日期 2026-09-25｜运行ID AGENT-20260925-085337</x:v>
+        <x:v>数据日期 2026-09-25｜运行ID AGENT-20260925-090621</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
@@ -465,7 +465,7 @@
       </x:c>
       <x:c r="B6" s="12" t="n">
         <x:f>COUNTA('发现清单'!$A$5:$A$204)</x:f>
-        <x:v>54</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C6" s="12" t="n">
         <x:f>COUNTIF('发现清单'!$C$5:$C$204,"重大")</x:f>
@@ -477,7 +477,7 @@
       </x:c>
       <x:c r="E6" s="12" t="n">
         <x:f>COUNTIF('发现清单'!$C$5:$C$204,"中")</x:f>
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F6" s="12" t="n">
         <x:f>COUNTIF('发现清单'!$I$5:$I$204,"是")</x:f>
@@ -485,7 +485,7 @@
       </x:c>
       <x:c r="G6" s="12" t="n">
         <x:f>COUNTIF('发现清单'!$M$5:$M$204,"待确认")</x:f>
-        <x:v>54</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
         <x:f>"只读建议"</x:f>
@@ -514,10 +514,10 @@
         <x:v>识别延期、近期到期和责任信息</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>26</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D10" s="10" t="str">
-        <x:v>识别26项进度关注事项</x:v>
+        <x:v>识别47项进度关注事项</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -650,7 +650,7 @@
         <x:v>红</x:v>
       </x:c>
       <x:c r="B6" s="12" t="n">
-        <x:v>54</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C6" s="12" t="n">
         <x:v>46</x:v>
@@ -659,7 +659,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E6" s="12" t="n">
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F6" s="12" t="n">
         <x:v>29</x:v>
@@ -880,7 +880,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F5" s="18" t="str">
-        <x:v>【连续第4期出现】汇编可研报告并组织评审计划完成日为2026-09-18，当前状态为进行中。</x:v>
+        <x:v>【连续第5期出现】汇编可研报告并组织评审计划完成日为2026-09-18，当前状态为进行中。</x:v>
       </x:c>
       <x:c r="G5" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -895,7 +895,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K5" s="10" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L5" s="10" t="str"/>
       <x:c r="M5" s="21" t="str">
@@ -905,37 +905,37 @@
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="10" t="str">
-        <x:v>SCH-T011-OVERDUE</x:v>
+        <x:v>SCH-T008-NORISK</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C6" s="22" t="str">
-        <x:v>重大</x:v>
+      <x:c r="C6" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D6" s="10" t="str">
-        <x:v>T011</x:v>
+        <x:v>T008</x:v>
       </x:c>
       <x:c r="E6" s="10" t="str">
-        <x:v>任务已延期</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F6" s="18" t="str">
-        <x:v>【连续第10期出现】盘点既有系统、接口与数据计划完成日为2026-05-05，当前状态为进行中。</x:v>
+        <x:v>汇编可研报告并组织评审（T008）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G6" s="18" t="str">
-        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H6" s="10" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="I6" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J6" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K6" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L6" s="10" t="str"/>
       <x:c r="M6" s="21" t="str">
@@ -945,7 +945,7 @@
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
       <x:c r="A7" s="10" t="str">
-        <x:v>SCH-T012-OVERDUE</x:v>
+        <x:v>SCH-T011-OVERDUE</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
         <x:v>进度资源Agent</x:v>
@@ -954,19 +954,19 @@
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D7" s="10" t="str">
-        <x:v>T012</x:v>
+        <x:v>T011</x:v>
       </x:c>
       <x:c r="E7" s="10" t="str">
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F7" s="18" t="str">
-        <x:v>【连续第10期出现】访谈业务部门并形成痛点清单计划完成日为2026-06-02，当前状态为待确认。</x:v>
+        <x:v>【连续第11期出现】盘点既有系统、接口与数据计划完成日为2026-05-05，当前状态为进行中。</x:v>
       </x:c>
       <x:c r="G7" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H7" s="10" t="str">
-        <x:v>产品经理</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="I7" s="10" t="str">
         <x:v>是</x:v>
@@ -975,7 +975,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K7" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L7" s="10" t="str"/>
       <x:c r="M7" s="21" t="str">
@@ -985,37 +985,37 @@
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="10" t="str">
-        <x:v>SCH-T013-OVERDUE</x:v>
+        <x:v>SCH-T011-NORISK</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C8" s="22" t="str">
-        <x:v>重大</x:v>
+      <x:c r="C8" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D8" s="10" t="str">
-        <x:v>T013</x:v>
+        <x:v>T011</x:v>
       </x:c>
       <x:c r="E8" s="10" t="str">
-        <x:v>任务已延期</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F8" s="18" t="str">
-        <x:v>【连续第10期出现】确认现状流程、问题与改进机会基线计划完成日为2026-06-30，当前状态为待确认。</x:v>
+        <x:v>盘点既有系统、接口与数据（T011）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G8" s="18" t="str">
-        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H8" s="10" t="str">
-        <x:v>项目经理</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J8" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K8" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L8" s="10" t="str"/>
       <x:c r="M8" s="21" t="str">
@@ -1025,7 +1025,7 @@
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="10" t="str">
-        <x:v>SCH-T014-OVERDUE</x:v>
+        <x:v>SCH-T012-OVERDUE</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
         <x:v>进度资源Agent</x:v>
@@ -1034,19 +1034,19 @@
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D9" s="10" t="str">
-        <x:v>T014</x:v>
+        <x:v>T012</x:v>
       </x:c>
       <x:c r="E9" s="10" t="str">
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F9" s="18" t="str">
-        <x:v>【连续第10期出现】制定项目治理、会议与报告机制计划完成日为2026-07-12，当前状态为待确认。</x:v>
+        <x:v>【连续第11期出现】访谈业务部门并形成痛点清单计划完成日为2026-06-02，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G9" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H9" s="10" t="str">
-        <x:v>项目经理</x:v>
+        <x:v>产品经理</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str">
         <x:v>是</x:v>
@@ -1055,7 +1055,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K9" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L9" s="10" t="str"/>
       <x:c r="M9" s="21" t="str">
@@ -1065,37 +1065,37 @@
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="10" t="str">
-        <x:v>SCH-T015-OVERDUE</x:v>
+        <x:v>SCH-T012-NORISK</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C10" s="22" t="str">
-        <x:v>重大</x:v>
+      <x:c r="C10" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D10" s="10" t="str">
-        <x:v>T015</x:v>
+        <x:v>T012</x:v>
       </x:c>
       <x:c r="E10" s="10" t="str">
-        <x:v>任务已延期</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F10" s="18" t="str">
-        <x:v>【连续第10期出现】制定需求分级、跟踪与变更规范计划完成日为2026-07-24，当前状态为待确认。</x:v>
+        <x:v>访谈业务部门并形成痛点清单（T012）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G10" s="18" t="str">
-        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H10" s="10" t="str">
         <x:v>产品经理</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J10" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K10" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L10" s="10" t="str"/>
       <x:c r="M10" s="21" t="str">
@@ -1105,7 +1105,7 @@
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="10" t="str">
-        <x:v>SCH-T016-OVERDUE</x:v>
+        <x:v>SCH-T013-OVERDUE</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
         <x:v>进度资源Agent</x:v>
@@ -1114,19 +1114,19 @@
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D11" s="10" t="str">
-        <x:v>T016</x:v>
+        <x:v>T013</x:v>
       </x:c>
       <x:c r="E11" s="10" t="str">
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F11" s="18" t="str">
-        <x:v>【连续第10期出现】制定设计、编码与代码评审规范计划完成日为2026-08-06，当前状态为待确认。</x:v>
+        <x:v>【连续第11期出现】确认现状流程、问题与改进机会基线计划完成日为2026-06-30，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G11" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H11" s="10" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str">
         <x:v>是</x:v>
@@ -1135,7 +1135,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K11" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L11" s="10" t="str"/>
       <x:c r="M11" s="21" t="str">
@@ -1145,37 +1145,37 @@
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="10" t="str">
-        <x:v>SCH-T017-OVERDUE</x:v>
+        <x:v>SCH-T013-NORISK</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="str">
-        <x:v>重大</x:v>
+      <x:c r="C12" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D12" s="10" t="str">
-        <x:v>T017</x:v>
+        <x:v>T013</x:v>
       </x:c>
       <x:c r="E12" s="10" t="str">
-        <x:v>任务已延期</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F12" s="18" t="str">
-        <x:v>【连续第10期出现】制定测试、缺陷与质量门禁规范计划完成日为2026-08-18，当前状态为待确认。</x:v>
+        <x:v>确认现状流程、问题与改进机会基线（T013）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G12" s="18" t="str">
-        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H12" s="10" t="str">
-        <x:v>高级测试人员、中级测试人员</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J12" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K12" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L12" s="10" t="str"/>
       <x:c r="M12" s="21" t="str">
@@ -1185,7 +1185,7 @@
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
       <x:c r="A13" s="10" t="str">
-        <x:v>SCH-T018-OVERDUE</x:v>
+        <x:v>SCH-T014-OVERDUE</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
         <x:v>进度资源Agent</x:v>
@@ -1194,19 +1194,19 @@
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D13" s="10" t="str">
-        <x:v>T018</x:v>
+        <x:v>T014</x:v>
       </x:c>
       <x:c r="E13" s="10" t="str">
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F13" s="18" t="str">
-        <x:v>【连续第10期出现】制定配置、发布与文档归档规范计划完成日为2026-08-31，当前状态为待确认。</x:v>
+        <x:v>【连续第11期出现】制定项目治理、会议与报告机制计划完成日为2026-07-12，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G13" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H13" s="10" t="str">
-        <x:v>配置人员</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
         <x:v>是</x:v>
@@ -1215,7 +1215,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K13" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L13" s="10" t="str"/>
       <x:c r="M13" s="21" t="str">
@@ -1225,37 +1225,37 @@
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="10" t="str">
-        <x:v>SCH-T019-OVERDUE</x:v>
+        <x:v>SCH-T014-NORISK</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="str">
-        <x:v>重大</x:v>
+      <x:c r="C14" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D14" s="10" t="str">
-        <x:v>T019</x:v>
+        <x:v>T014</x:v>
       </x:c>
       <x:c r="E14" s="10" t="str">
-        <x:v>任务已延期</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F14" s="18" t="str">
-        <x:v>【连续第10期出现】完成系统分层、模块与服务边界设计计划完成日为2026-07-15，当前状态为待确认。</x:v>
+        <x:v>制定项目治理、会议与报告机制（T014）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G14" s="18" t="str">
-        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H14" s="10" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J14" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K14" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L14" s="10" t="str"/>
       <x:c r="M14" s="21" t="str">
@@ -1265,7 +1265,7 @@
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
       <x:c r="A15" s="10" t="str">
-        <x:v>SCH-T020-OVERDUE</x:v>
+        <x:v>SCH-T015-OVERDUE</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
         <x:v>进度资源Agent</x:v>
@@ -1274,19 +1274,19 @@
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D15" s="10" t="str">
-        <x:v>T020</x:v>
+        <x:v>T015</x:v>
       </x:c>
       <x:c r="E15" s="10" t="str">
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F15" s="18" t="str">
-        <x:v>【连续第10期出现】完成主数据、交易数据与分析数据架构计划完成日为2026-07-30，当前状态为待确认。</x:v>
+        <x:v>【连续第11期出现】制定需求分级、跟踪与变更规范计划完成日为2026-07-24，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G15" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H15" s="10" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>产品经理</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str">
         <x:v>是</x:v>
@@ -1295,7 +1295,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K15" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L15" s="10" t="str"/>
       <x:c r="M15" s="21" t="str">
@@ -1305,37 +1305,37 @@
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="10" t="str">
-        <x:v>SCH-T021-OVERDUE</x:v>
+        <x:v>SCH-T015-NORISK</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C16" s="22" t="str">
-        <x:v>重大</x:v>
+      <x:c r="C16" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D16" s="10" t="str">
-        <x:v>T021</x:v>
+        <x:v>T015</x:v>
       </x:c>
       <x:c r="E16" s="10" t="str">
-        <x:v>任务已延期</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F16" s="18" t="str">
-        <x:v>【连续第10期出现】完成内部及外部接口总体架构计划完成日为2026-08-15，当前状态为待确认。</x:v>
+        <x:v>制定需求分级、跟踪与变更规范（T015）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G16" s="18" t="str">
-        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H16" s="10" t="str">
-        <x:v>高级开发人员</x:v>
+        <x:v>产品经理</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J16" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K16" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L16" s="10" t="str"/>
       <x:c r="M16" s="21" t="str">
@@ -1345,7 +1345,7 @@
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="10" t="str">
-        <x:v>SCH-T022-OVERDUE</x:v>
+        <x:v>SCH-T016-OVERDUE</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
         <x:v>进度资源Agent</x:v>
@@ -1354,13 +1354,13 @@
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D17" s="10" t="str">
-        <x:v>T022</x:v>
+        <x:v>T016</x:v>
       </x:c>
       <x:c r="E17" s="10" t="str">
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F17" s="18" t="str">
-        <x:v>【连续第10期出现】完成身份、权限、审计与数据安全设计计划完成日为2026-08-30，当前状态为待确认。</x:v>
+        <x:v>【连续第11期出现】制定设计、编码与代码评审规范计划完成日为2026-08-06，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G17" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1375,7 +1375,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K17" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L17" s="10" t="str"/>
       <x:c r="M17" s="21" t="str">
@@ -1385,37 +1385,37 @@
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="10" t="str">
-        <x:v>SCH-T023-OVERDUE</x:v>
+        <x:v>SCH-T016-NORISK</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C18" s="22" t="str">
-        <x:v>重大</x:v>
+      <x:c r="C18" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D18" s="10" t="str">
-        <x:v>T023</x:v>
+        <x:v>T016</x:v>
       </x:c>
       <x:c r="E18" s="10" t="str">
-        <x:v>任务已延期</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F18" s="18" t="str">
-        <x:v>【连续第10期出现】完成环境、网络、容灾和DevOps设计计划完成日为2026-09-14，当前状态为待确认。</x:v>
+        <x:v>制定设计、编码与代码评审规范（T016）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G18" s="18" t="str">
-        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H18" s="10" t="str">
-        <x:v>配置人员</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J18" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K18" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L18" s="10" t="str"/>
       <x:c r="M18" s="21" t="str">
@@ -1425,37 +1425,37 @@
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
       <x:c r="A19" s="10" t="str">
-        <x:v>SCH-T024-DUE14</x:v>
+        <x:v>SCH-T017-OVERDUE</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C19" s="23" t="str">
-        <x:v>高</x:v>
+      <x:c r="C19" s="22" t="str">
+        <x:v>重大</x:v>
       </x:c>
       <x:c r="D19" s="10" t="str">
-        <x:v>T024</x:v>
+        <x:v>T017</x:v>
       </x:c>
       <x:c r="E19" s="10" t="str">
-        <x:v>任务14天内到期</x:v>
+        <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F19" s="18" t="str">
-        <x:v>【连续第10期出现】汇编总体技术架构并完成基线评审将在2026-09-30到期，当前状态为进行中。</x:v>
+        <x:v>【连续第11期出现】制定测试、缺陷与质量门禁规范计划完成日为2026-08-18，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G19" s="18" t="str">
-        <x:v>确认交付物、验收人和按期完成证据。</x:v>
+        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H19" s="10" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="J19" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K19" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L19" s="10" t="str"/>
       <x:c r="M19" s="21" t="str">
@@ -1465,37 +1465,37 @@
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="10" t="str">
-        <x:v>SCH-T025-OVERDUE</x:v>
+        <x:v>SCH-T017-NORISK</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C20" s="22" t="str">
-        <x:v>重大</x:v>
+      <x:c r="C20" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D20" s="10" t="str">
-        <x:v>T025</x:v>
+        <x:v>T017</x:v>
       </x:c>
       <x:c r="E20" s="10" t="str">
-        <x:v>任务已延期</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F20" s="18" t="str">
-        <x:v>【连续第10期出现】编制CA、电子文档、BI报表POC方案与评分标准计划完成日为2026-08-19，当前状态为待确认。</x:v>
+        <x:v>制定测试、缺陷与质量门禁规范（T017）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G20" s="18" t="str">
-        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H20" s="10" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J20" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K20" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L20" s="10" t="str"/>
       <x:c r="M20" s="21" t="str">
@@ -1505,7 +1505,7 @@
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
       <x:c r="A21" s="10" t="str">
-        <x:v>SCH-T026-OVERDUE</x:v>
+        <x:v>SCH-T018-OVERDUE</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
         <x:v>进度资源Agent</x:v>
@@ -1514,19 +1514,19 @@
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D21" s="10" t="str">
-        <x:v>T026</x:v>
+        <x:v>T018</x:v>
       </x:c>
       <x:c r="E21" s="10" t="str">
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F21" s="18" t="str">
-        <x:v>【连续第10期出现】验证证书签发、身份认证和证书管理计划完成日为2026-08-24，当前状态为待确认。</x:v>
+        <x:v>【连续第11期出现】制定配置、发布与文档归档规范计划完成日为2026-08-31，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G21" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H21" s="10" t="str">
-        <x:v>高级开发人员</x:v>
+        <x:v>配置人员</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str">
         <x:v>是</x:v>
@@ -1535,7 +1535,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K21" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L21" s="10" t="str"/>
       <x:c r="M21" s="21" t="str">
@@ -1545,37 +1545,37 @@
     </x:row>
     <x:row r="22" ht="42" customHeight="1">
       <x:c r="A22" s="10" t="str">
-        <x:v>SCH-T027-OVERDUE</x:v>
+        <x:v>SCH-T018-NORISK</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C22" s="22" t="str">
-        <x:v>重大</x:v>
+      <x:c r="C22" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D22" s="10" t="str">
-        <x:v>T027</x:v>
+        <x:v>T018</x:v>
       </x:c>
       <x:c r="E22" s="10" t="str">
-        <x:v>任务已延期</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F22" s="18" t="str">
-        <x:v>【连续第10期出现】验证电子签名、验签、时间戳和审计追溯计划完成日为2026-08-29，当前状态为待确认。</x:v>
+        <x:v>制定配置、发布与文档归档规范（T018）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G22" s="18" t="str">
-        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H22" s="10" t="str">
-        <x:v>高级测试人员、中级测试人员</x:v>
+        <x:v>配置人员</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J22" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K22" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L22" s="10" t="str"/>
       <x:c r="M22" s="21" t="str">
@@ -1585,7 +1585,7 @@
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
       <x:c r="A23" s="10" t="str">
-        <x:v>SCH-T028-OVERDUE</x:v>
+        <x:v>SCH-T019-OVERDUE</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
         <x:v>进度资源Agent</x:v>
@@ -1594,19 +1594,19 @@
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D23" s="10" t="str">
-        <x:v>T028</x:v>
+        <x:v>T019</x:v>
       </x:c>
       <x:c r="E23" s="10" t="str">
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F23" s="18" t="str">
-        <x:v>【连续第10期出现】验证模板生成、在线预览和格式转换计划完成日为2026-09-04，当前状态为待确认。</x:v>
+        <x:v>【连续第11期出现】完成系统分层、模块与服务边界设计计划完成日为2026-07-15，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G23" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H23" s="10" t="str">
-        <x:v>中级开发人员</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str">
         <x:v>是</x:v>
@@ -1615,7 +1615,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K23" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L23" s="10" t="str"/>
       <x:c r="M23" s="21" t="str">
@@ -1625,37 +1625,37 @@
     </x:row>
     <x:row r="24" ht="42" customHeight="1">
       <x:c r="A24" s="10" t="str">
-        <x:v>SCH-T029-OVERDUE</x:v>
+        <x:v>SCH-T019-NORISK</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C24" s="22" t="str">
-        <x:v>重大</x:v>
+      <x:c r="C24" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D24" s="10" t="str">
-        <x:v>T029</x:v>
+        <x:v>T019</x:v>
       </x:c>
       <x:c r="E24" s="10" t="str">
-        <x:v>任务已延期</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F24" s="18" t="str">
-        <x:v>【连续第10期出现】验证水印、权限控制、归档和大文件性能计划完成日为2026-09-09，当前状态为待确认。</x:v>
+        <x:v>完成系统分层、模块与服务边界设计（T019）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G24" s="18" t="str">
-        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H24" s="10" t="str">
-        <x:v>高级测试人员、中级测试人员</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J24" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K24" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L24" s="10" t="str"/>
       <x:c r="M24" s="21" t="str">
@@ -1665,7 +1665,7 @@
     </x:row>
     <x:row r="25" ht="42" customHeight="1">
       <x:c r="A25" s="10" t="str">
-        <x:v>SCH-T030-OVERDUE</x:v>
+        <x:v>SCH-T020-OVERDUE</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
         <x:v>进度资源Agent</x:v>
@@ -1674,19 +1674,19 @@
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D25" s="10" t="str">
-        <x:v>T030</x:v>
+        <x:v>T020</x:v>
       </x:c>
       <x:c r="E25" s="10" t="str">
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F25" s="18" t="str">
-        <x:v>【连续第10期出现】验证数据接入、指标模型和经营报表计划完成日为2026-09-14，当前状态为待确认。</x:v>
+        <x:v>【连续第11期出现】完成主数据、交易数据与分析数据架构计划完成日为2026-07-30，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G25" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H25" s="10" t="str">
-        <x:v>高级开发人员</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str">
         <x:v>是</x:v>
@@ -1695,7 +1695,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K25" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L25" s="10" t="str"/>
       <x:c r="M25" s="21" t="str">
@@ -1705,37 +1705,37 @@
     </x:row>
     <x:row r="26" ht="42" customHeight="1">
       <x:c r="A26" s="10" t="str">
-        <x:v>SCH-T031-OVERDUE</x:v>
+        <x:v>SCH-T020-NORISK</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C26" s="22" t="str">
-        <x:v>重大</x:v>
+      <x:c r="C26" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D26" s="10" t="str">
-        <x:v>T031</x:v>
+        <x:v>T020</x:v>
       </x:c>
       <x:c r="E26" s="10" t="str">
-        <x:v>任务已延期</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F26" s="18" t="str">
-        <x:v>【连续第4期出现】验证权限、钻取、导出和查询性能计划完成日为2026-09-19，当前状态为进行中。</x:v>
+        <x:v>完成主数据、交易数据与分析数据架构（T020）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G26" s="18" t="str">
-        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H26" s="10" t="str">
-        <x:v>高级测试人员、中级测试人员</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J26" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K26" s="10" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L26" s="10" t="str"/>
       <x:c r="M26" s="21" t="str">
@@ -1745,37 +1745,37 @@
     </x:row>
     <x:row r="27" ht="42" customHeight="1">
       <x:c r="A27" s="10" t="str">
-        <x:v>SCH-T032-DUE14</x:v>
+        <x:v>SCH-T021-OVERDUE</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C27" s="23" t="str">
-        <x:v>高</x:v>
+      <x:c r="C27" s="22" t="str">
+        <x:v>重大</x:v>
       </x:c>
       <x:c r="D27" s="10" t="str">
-        <x:v>T032</x:v>
+        <x:v>T021</x:v>
       </x:c>
       <x:c r="E27" s="10" t="str">
-        <x:v>任务14天内到期</x:v>
+        <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F27" s="18" t="str">
-        <x:v>【连续第10期出现】汇总问题清单、适配结论和产品选型建议将在2026-09-25到期，当前状态为未开始。</x:v>
+        <x:v>【连续第11期出现】完成内部及外部接口总体架构计划完成日为2026-08-15，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G27" s="18" t="str">
-        <x:v>确认交付物、验收人和按期完成证据。</x:v>
+        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H27" s="10" t="str">
-        <x:v>项目经理</x:v>
+        <x:v>高级开发人员</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="J27" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K27" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L27" s="10" t="str"/>
       <x:c r="M27" s="21" t="str">
@@ -1785,28 +1785,28 @@
     </x:row>
     <x:row r="28" ht="42" customHeight="1">
       <x:c r="A28" s="10" t="str">
-        <x:v>SCH-T033-DUE14</x:v>
+        <x:v>SCH-T021-NORISK</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C28" s="23" t="str">
-        <x:v>高</x:v>
+      <x:c r="C28" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D28" s="10" t="str">
-        <x:v>T033</x:v>
+        <x:v>T021</x:v>
       </x:c>
       <x:c r="E28" s="10" t="str">
-        <x:v>任务14天内到期</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F28" s="18" t="str">
-        <x:v>【连续第10期出现】编制并审批项目章程将在2026-10-02到期，当前状态为未开始。</x:v>
+        <x:v>完成内部及外部接口总体架构（T021）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G28" s="18" t="str">
-        <x:v>确认交付物、验收人和按期完成证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H28" s="10" t="str">
-        <x:v>项目集经理</x:v>
+        <x:v>高级开发人员</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str">
         <x:v>否</x:v>
@@ -1815,7 +1815,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K28" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L28" s="10" t="str"/>
       <x:c r="M28" s="21" t="str">
@@ -1825,37 +1825,37 @@
     </x:row>
     <x:row r="29" ht="42" customHeight="1">
       <x:c r="A29" s="10" t="str">
-        <x:v>SCH-T034-DUE14</x:v>
+        <x:v>SCH-T022-OVERDUE</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C29" s="23" t="str">
-        <x:v>高</x:v>
+      <x:c r="C29" s="22" t="str">
+        <x:v>重大</x:v>
       </x:c>
       <x:c r="D29" s="10" t="str">
-        <x:v>T034</x:v>
+        <x:v>T022</x:v>
       </x:c>
       <x:c r="E29" s="10" t="str">
-        <x:v>任务14天内到期</x:v>
+        <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F29" s="18" t="str">
-        <x:v>【连续第4期出现】编制范围、里程碑和主进度计划将在2026-10-05到期，当前状态为未开始。</x:v>
+        <x:v>【连续第11期出现】完成身份、权限、审计与数据安全设计计划完成日为2026-08-30，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G29" s="18" t="str">
-        <x:v>确认交付物、验收人和按期完成证据。</x:v>
+        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H29" s="10" t="str">
-        <x:v>项目经理</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="J29" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K29" s="10" t="n">
-        <x:v>4</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L29" s="10" t="str"/>
       <x:c r="M29" s="21" t="str">
@@ -1865,28 +1865,28 @@
     </x:row>
     <x:row r="30" ht="42" customHeight="1">
       <x:c r="A30" s="10" t="str">
-        <x:v>SCH-T035-DUE14</x:v>
+        <x:v>SCH-T022-NORISK</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
         <x:v>进度资源Agent</x:v>
       </x:c>
-      <x:c r="C30" s="23" t="str">
-        <x:v>高</x:v>
+      <x:c r="C30" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D30" s="10" t="str">
-        <x:v>T035</x:v>
+        <x:v>T022</x:v>
       </x:c>
       <x:c r="E30" s="10" t="str">
-        <x:v>任务14天内到期</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F30" s="18" t="str">
-        <x:v>【连续第3期出现】建立项目组织、RACI与沟通机制将在2026-10-08到期，当前状态为未开始。</x:v>
+        <x:v>完成身份、权限、审计与数据安全设计（T022）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G30" s="18" t="str">
-        <x:v>确认交付物、验收人和按期完成证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H30" s="10" t="str">
-        <x:v>项目经理</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str">
         <x:v>否</x:v>
@@ -1895,7 +1895,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K30" s="10" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L30" s="10" t="str"/>
       <x:c r="M30" s="21" t="str">
@@ -1905,37 +1905,37 @@
     </x:row>
     <x:row r="31" ht="42" customHeight="1">
       <x:c r="A31" s="10" t="str">
-        <x:v>RSK-RSK-001</x:v>
+        <x:v>SCH-T023-OVERDUE</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
+        <x:v>进度资源Agent</x:v>
       </x:c>
       <x:c r="C31" s="22" t="str">
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D31" s="10" t="str">
-        <x:v>RSK-001</x:v>
+        <x:v>T023</x:v>
       </x:c>
       <x:c r="E31" s="10" t="str">
-        <x:v>高剩余风险</x:v>
+        <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F31" s="18" t="str">
-        <x:v>【连续第10期出现】CA、电子文档、BI产品POC与选型未按期完成</x:v>
+        <x:v>【连续第11期出现】完成环境、网络、容灾和DevOps设计计划完成日为2026-09-14，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G31" s="18" t="str">
-        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
+        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H31" s="10" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>配置人员</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="J31" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K31" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L31" s="10" t="str"/>
       <x:c r="M31" s="21" t="str">
@@ -1945,28 +1945,28 @@
     </x:row>
     <x:row r="32" ht="42" customHeight="1">
       <x:c r="A32" s="10" t="str">
-        <x:v>RSK-RSK-002</x:v>
+        <x:v>SCH-T023-NORISK</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
-      </x:c>
-      <x:c r="C32" s="22" t="str">
-        <x:v>重大</x:v>
+        <x:v>进度资源Agent</x:v>
+      </x:c>
+      <x:c r="C32" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D32" s="10" t="str">
-        <x:v>RSK-002</x:v>
+        <x:v>T023</x:v>
       </x:c>
       <x:c r="E32" s="10" t="str">
-        <x:v>高剩余风险</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F32" s="18" t="str">
-        <x:v>【连续第10期出现】总体技术架构基线未通过评审</x:v>
+        <x:v>完成环境、网络、容灾和DevOps设计（T023）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G32" s="18" t="str">
-        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H32" s="10" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>配置人员</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
         <x:v>否</x:v>
@@ -1975,7 +1975,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K32" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L32" s="10" t="str"/>
       <x:c r="M32" s="21" t="str">
@@ -1985,28 +1985,28 @@
     </x:row>
     <x:row r="33" ht="42" customHeight="1">
       <x:c r="A33" s="10" t="str">
-        <x:v>RSK-RSK-003</x:v>
+        <x:v>SCH-T024-DUE14</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
-      </x:c>
-      <x:c r="C33" s="22" t="str">
-        <x:v>重大</x:v>
+        <x:v>进度资源Agent</x:v>
+      </x:c>
+      <x:c r="C33" s="23" t="str">
+        <x:v>高</x:v>
       </x:c>
       <x:c r="D33" s="10" t="str">
-        <x:v>RSK-003</x:v>
+        <x:v>T024</x:v>
       </x:c>
       <x:c r="E33" s="10" t="str">
-        <x:v>高剩余风险</x:v>
+        <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F33" s="18" t="str">
-        <x:v>【连续第10期出现】外部系统接口边界与联调窗口不明确</x:v>
+        <x:v>【连续第11期出现】汇编总体技术架构并完成基线评审将在2026-09-30到期，当前状态为进行中。</x:v>
       </x:c>
       <x:c r="G33" s="18" t="str">
-        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
+        <x:v>确认交付物、验收人和按期完成证据。</x:v>
       </x:c>
       <x:c r="H33" s="10" t="str">
-        <x:v>项目经理</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="I33" s="10" t="str">
         <x:v>否</x:v>
@@ -2015,7 +2015,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K33" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L33" s="10" t="str"/>
       <x:c r="M33" s="21" t="str">
@@ -2025,25 +2025,25 @@
     </x:row>
     <x:row r="34" ht="42" customHeight="1">
       <x:c r="A34" s="10" t="str">
-        <x:v>RSK-RSK-004</x:v>
+        <x:v>SCH-T025-OVERDUE</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
+        <x:v>进度资源Agent</x:v>
       </x:c>
       <x:c r="C34" s="22" t="str">
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D34" s="10" t="str">
-        <x:v>RSK-004</x:v>
+        <x:v>T025</x:v>
       </x:c>
       <x:c r="E34" s="10" t="str">
-        <x:v>重大剩余风险</x:v>
+        <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F34" s="18" t="str">
-        <x:v>【连续第10期出现】安全合规基线未形成或外部产品不满足要求</x:v>
+        <x:v>【连续第11期出现】编制CA、电子文档、BI报表POC方案与评分标准计划完成日为2026-08-19，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G34" s="18" t="str">
-        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
+        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H34" s="10" t="str">
         <x:v>技术经理</x:v>
@@ -2055,7 +2055,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K34" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L34" s="10" t="str"/>
       <x:c r="M34" s="21" t="str">
@@ -2065,28 +2065,28 @@
     </x:row>
     <x:row r="35" ht="42" customHeight="1">
       <x:c r="A35" s="10" t="str">
-        <x:v>RSK-RSK-005</x:v>
+        <x:v>SCH-T025-NORISK</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
-      </x:c>
-      <x:c r="C35" s="22" t="str">
-        <x:v>重大</x:v>
+        <x:v>进度资源Agent</x:v>
+      </x:c>
+      <x:c r="C35" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D35" s="10" t="str">
-        <x:v>RSK-005</x:v>
+        <x:v>T025</x:v>
       </x:c>
       <x:c r="E35" s="10" t="str">
-        <x:v>高剩余风险</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F35" s="18" t="str">
-        <x:v>【连续第10期出现】30人团队未按阶段计划到位</x:v>
+        <x:v>编制CA、电子文档、BI报表POC方案与评分标准（T025）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G35" s="18" t="str">
-        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H35" s="10" t="str">
-        <x:v>项目集经理</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str">
         <x:v>否</x:v>
@@ -2095,7 +2095,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K35" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L35" s="10" t="str"/>
       <x:c r="M35" s="21" t="str">
@@ -2105,37 +2105,37 @@
     </x:row>
     <x:row r="36" ht="42" customHeight="1">
       <x:c r="A36" s="10" t="str">
-        <x:v>RSK-RSK-006</x:v>
+        <x:v>SCH-T026-OVERDUE</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
+        <x:v>进度资源Agent</x:v>
       </x:c>
       <x:c r="C36" s="22" t="str">
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D36" s="10" t="str">
-        <x:v>RSK-006</x:v>
+        <x:v>T026</x:v>
       </x:c>
       <x:c r="E36" s="10" t="str">
-        <x:v>高剩余风险</x:v>
+        <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F36" s="18" t="str">
-        <x:v>【连续第10期出现】一期范围与需求基线未确认</x:v>
+        <x:v>【连续第11期出现】验证证书签发、身份认证和证书管理计划完成日为2026-08-24，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G36" s="18" t="str">
-        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
+        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H36" s="10" t="str">
-        <x:v>产品经理</x:v>
+        <x:v>高级开发人员</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="J36" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K36" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L36" s="10" t="str"/>
       <x:c r="M36" s="21" t="str">
@@ -2145,28 +2145,28 @@
     </x:row>
     <x:row r="37" ht="42" customHeight="1">
       <x:c r="A37" s="10" t="str">
-        <x:v>RSK-RSK-007</x:v>
+        <x:v>SCH-T026-NORISK</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
-      </x:c>
-      <x:c r="C37" s="22" t="str">
-        <x:v>重大</x:v>
+        <x:v>进度资源Agent</x:v>
+      </x:c>
+      <x:c r="C37" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D37" s="10" t="str">
-        <x:v>RSK-007</x:v>
+        <x:v>T026</x:v>
       </x:c>
       <x:c r="E37" s="10" t="str">
-        <x:v>高剩余风险</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F37" s="18" t="str">
-        <x:v>【连续第10期出现】历史合同数据质量不足或迁移范围失控</x:v>
+        <x:v>验证证书签发、身份认证和证书管理（T026）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G37" s="18" t="str">
-        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H37" s="10" t="str">
-        <x:v>产品经理</x:v>
+        <x:v>高级开发人员</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str">
         <x:v>否</x:v>
@@ -2175,7 +2175,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K37" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L37" s="10" t="str"/>
       <x:c r="M37" s="21" t="str">
@@ -2185,37 +2185,37 @@
     </x:row>
     <x:row r="38" ht="42" customHeight="1">
       <x:c r="A38" s="10" t="str">
-        <x:v>RSK-RSK-008</x:v>
+        <x:v>SCH-T027-OVERDUE</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
+        <x:v>进度资源Agent</x:v>
       </x:c>
       <x:c r="C38" s="22" t="str">
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D38" s="10" t="str">
-        <x:v>RSK-008</x:v>
+        <x:v>T027</x:v>
       </x:c>
       <x:c r="E38" s="10" t="str">
-        <x:v>高剩余风险</x:v>
+        <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F38" s="18" t="str">
-        <x:v>【连续第10期出现】外部产品采购与合同条款不能支撑项目计划</x:v>
+        <x:v>【连续第11期出现】验证电子签名、验签、时间戳和审计追溯计划完成日为2026-08-29，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G38" s="18" t="str">
-        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
+        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H38" s="10" t="str">
-        <x:v>项目集经理</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="J38" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K38" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L38" s="10" t="str"/>
       <x:c r="M38" s="21" t="str">
@@ -2225,28 +2225,28 @@
     </x:row>
     <x:row r="39" ht="42" customHeight="1">
       <x:c r="A39" s="10" t="str">
-        <x:v>RSK-RSK-009</x:v>
+        <x:v>SCH-T027-NORISK</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
-      </x:c>
-      <x:c r="C39" s="22" t="str">
-        <x:v>重大</x:v>
+        <x:v>进度资源Agent</x:v>
+      </x:c>
+      <x:c r="C39" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D39" s="10" t="str">
-        <x:v>RSK-009</x:v>
+        <x:v>T027</x:v>
       </x:c>
       <x:c r="E39" s="10" t="str">
-        <x:v>高剩余风险</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F39" s="18" t="str">
-        <x:v>【连续第10期出现】项目章程和整体管理计划未正式批准</x:v>
+        <x:v>验证电子签名、验签、时间戳和审计追溯（T027）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G39" s="18" t="str">
-        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H39" s="10" t="str">
-        <x:v>项目集经理</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="I39" s="10" t="str">
         <x:v>否</x:v>
@@ -2255,7 +2255,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K39" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L39" s="10" t="str"/>
       <x:c r="M39" s="21" t="str">
@@ -2265,37 +2265,37 @@
     </x:row>
     <x:row r="40" ht="42" customHeight="1">
       <x:c r="A40" s="10" t="str">
-        <x:v>ISS-G10</x:v>
+        <x:v>SCH-T028-OVERDUE</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
+        <x:v>进度资源Agent</x:v>
       </x:c>
       <x:c r="C40" s="22" t="str">
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D40" s="10" t="str">
-        <x:v>G10</x:v>
+        <x:v>T028</x:v>
       </x:c>
       <x:c r="E40" s="10" t="str">
-        <x:v>未关闭问题</x:v>
+        <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F40" s="18" t="str">
-        <x:v>【连续第10期出现】CA、电子文档、BI产品POC与选型未按期完成：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第11期出现】验证模板生成、在线预览和格式转换计划完成日为2026-09-04，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G40" s="18" t="str">
-        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H40" s="10" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>中级开发人员</x:v>
       </x:c>
       <x:c r="I40" s="10" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="J40" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K40" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L40" s="10" t="str"/>
       <x:c r="M40" s="21" t="str">
@@ -2305,28 +2305,28 @@
     </x:row>
     <x:row r="41" ht="42" customHeight="1">
       <x:c r="A41" s="10" t="str">
-        <x:v>ISS-G09</x:v>
+        <x:v>SCH-T028-NORISK</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
-      </x:c>
-      <x:c r="C41" s="22" t="str">
-        <x:v>重大</x:v>
+        <x:v>进度资源Agent</x:v>
+      </x:c>
+      <x:c r="C41" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D41" s="10" t="str">
-        <x:v>G09</x:v>
+        <x:v>T028</x:v>
       </x:c>
       <x:c r="E41" s="10" t="str">
-        <x:v>未关闭问题</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F41" s="18" t="str">
-        <x:v>【连续第10期出现】总体技术架构基线未通过评审：需在正式启动前完成证据确认</x:v>
+        <x:v>验证模板生成、在线预览和格式转换（T028）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G41" s="18" t="str">
-        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H41" s="10" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>中级开发人员</x:v>
       </x:c>
       <x:c r="I41" s="10" t="str">
         <x:v>否</x:v>
@@ -2335,7 +2335,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K41" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L41" s="10" t="str"/>
       <x:c r="M41" s="21" t="str">
@@ -2345,37 +2345,37 @@
     </x:row>
     <x:row r="42" ht="42" customHeight="1">
       <x:c r="A42" s="10" t="str">
-        <x:v>ISS-G19</x:v>
+        <x:v>SCH-T029-OVERDUE</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
+        <x:v>进度资源Agent</x:v>
       </x:c>
       <x:c r="C42" s="22" t="str">
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D42" s="10" t="str">
-        <x:v>G19</x:v>
+        <x:v>T029</x:v>
       </x:c>
       <x:c r="E42" s="10" t="str">
-        <x:v>未关闭问题</x:v>
+        <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F42" s="18" t="str">
-        <x:v>【连续第10期出现】外部系统接口边界与联调窗口不明确：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第11期出现】验证水印、权限控制、归档和大文件性能计划完成日为2026-09-09，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G42" s="18" t="str">
-        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H42" s="10" t="str">
-        <x:v>项目经理</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="I42" s="10" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="J42" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K42" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L42" s="10" t="str"/>
       <x:c r="M42" s="21" t="str">
@@ -2385,28 +2385,28 @@
     </x:row>
     <x:row r="43" ht="42" customHeight="1">
       <x:c r="A43" s="10" t="str">
-        <x:v>ISS-G16</x:v>
+        <x:v>SCH-T029-NORISK</x:v>
       </x:c>
       <x:c r="B43" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
-      </x:c>
-      <x:c r="C43" s="22" t="str">
-        <x:v>重大</x:v>
+        <x:v>进度资源Agent</x:v>
+      </x:c>
+      <x:c r="C43" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D43" s="10" t="str">
-        <x:v>G16</x:v>
+        <x:v>T029</x:v>
       </x:c>
       <x:c r="E43" s="10" t="str">
-        <x:v>未关闭问题</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F43" s="18" t="str">
-        <x:v>【连续第10期出现】安全合规基线未形成或外部产品不满足要求：需在正式启动前完成证据确认</x:v>
+        <x:v>验证水印、权限控制、归档和大文件性能（T029）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G43" s="18" t="str">
-        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H43" s="10" t="str">
-        <x:v>技术经理</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="I43" s="10" t="str">
         <x:v>否</x:v>
@@ -2415,7 +2415,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K43" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L43" s="10" t="str"/>
       <x:c r="M43" s="21" t="str">
@@ -2425,37 +2425,37 @@
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
       <x:c r="A44" s="10" t="str">
-        <x:v>ISS-G08</x:v>
+        <x:v>SCH-T030-OVERDUE</x:v>
       </x:c>
       <x:c r="B44" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
+        <x:v>进度资源Agent</x:v>
       </x:c>
       <x:c r="C44" s="22" t="str">
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D44" s="10" t="str">
-        <x:v>G08</x:v>
+        <x:v>T030</x:v>
       </x:c>
       <x:c r="E44" s="10" t="str">
-        <x:v>未关闭问题</x:v>
+        <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F44" s="18" t="str">
-        <x:v>【连续第10期出现】30人团队未按阶段计划到位：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第11期出现】验证数据接入、指标模型和经营报表计划完成日为2026-09-14，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G44" s="18" t="str">
-        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H44" s="10" t="str">
-        <x:v>项目集经理</x:v>
+        <x:v>高级开发人员</x:v>
       </x:c>
       <x:c r="I44" s="10" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="J44" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K44" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L44" s="10" t="str"/>
       <x:c r="M44" s="21" t="str">
@@ -2465,28 +2465,28 @@
     </x:row>
     <x:row r="45" ht="42" customHeight="1">
       <x:c r="A45" s="10" t="str">
-        <x:v>ISS-G03/G11</x:v>
+        <x:v>SCH-T030-NORISK</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
-      </x:c>
-      <x:c r="C45" s="22" t="str">
-        <x:v>重大</x:v>
+        <x:v>进度资源Agent</x:v>
+      </x:c>
+      <x:c r="C45" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D45" s="10" t="str">
-        <x:v>G03/G11</x:v>
+        <x:v>T030</x:v>
       </x:c>
       <x:c r="E45" s="10" t="str">
-        <x:v>未关闭问题</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F45" s="18" t="str">
-        <x:v>【连续第10期出现】一期范围与需求基线未确认：需在正式启动前完成证据确认</x:v>
+        <x:v>验证数据接入、指标模型和经营报表（T030）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G45" s="18" t="str">
-        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H45" s="10" t="str">
-        <x:v>产品经理</x:v>
+        <x:v>高级开发人员</x:v>
       </x:c>
       <x:c r="I45" s="10" t="str">
         <x:v>否</x:v>
@@ -2495,7 +2495,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K45" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L45" s="10" t="str"/>
       <x:c r="M45" s="21" t="str">
@@ -2505,37 +2505,37 @@
     </x:row>
     <x:row r="46" ht="42" customHeight="1">
       <x:c r="A46" s="10" t="str">
-        <x:v>ISS-G15</x:v>
+        <x:v>SCH-T031-OVERDUE</x:v>
       </x:c>
       <x:c r="B46" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
+        <x:v>进度资源Agent</x:v>
       </x:c>
       <x:c r="C46" s="22" t="str">
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D46" s="10" t="str">
-        <x:v>G15</x:v>
+        <x:v>T031</x:v>
       </x:c>
       <x:c r="E46" s="10" t="str">
-        <x:v>未关闭问题</x:v>
+        <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F46" s="18" t="str">
-        <x:v>【连续第10期出现】历史合同数据质量不足或迁移范围失控：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第5期出现】验证权限、钻取、导出和查询性能计划完成日为2026-09-19，当前状态为进行中。</x:v>
       </x:c>
       <x:c r="G46" s="18" t="str">
-        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+        <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
       </x:c>
       <x:c r="H46" s="10" t="str">
-        <x:v>产品经理</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="I46" s="10" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="J46" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K46" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L46" s="10" t="str"/>
       <x:c r="M46" s="21" t="str">
@@ -2545,28 +2545,28 @@
     </x:row>
     <x:row r="47" ht="42" customHeight="1">
       <x:c r="A47" s="10" t="str">
-        <x:v>ISS-G14</x:v>
+        <x:v>SCH-T031-NORISK</x:v>
       </x:c>
       <x:c r="B47" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
-      </x:c>
-      <x:c r="C47" s="22" t="str">
-        <x:v>重大</x:v>
+        <x:v>进度资源Agent</x:v>
+      </x:c>
+      <x:c r="C47" s="21" t="str">
+        <x:v>中</x:v>
       </x:c>
       <x:c r="D47" s="10" t="str">
-        <x:v>G14</x:v>
+        <x:v>T031</x:v>
       </x:c>
       <x:c r="E47" s="10" t="str">
-        <x:v>未关闭问题</x:v>
+        <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F47" s="18" t="str">
-        <x:v>【连续第10期出现】外部产品采购与合同条款不能支撑项目计划：需在正式启动前完成证据确认</x:v>
+        <x:v>验证权限、钻取、导出和查询性能（T031）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G47" s="18" t="str">
-        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+        <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
       </x:c>
       <x:c r="H47" s="10" t="str">
-        <x:v>项目集经理</x:v>
+        <x:v>高级测试人员、中级测试人员</x:v>
       </x:c>
       <x:c r="I47" s="10" t="str">
         <x:v>否</x:v>
@@ -2575,7 +2575,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K47" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L47" s="10" t="str"/>
       <x:c r="M47" s="21" t="str">
@@ -2585,28 +2585,28 @@
     </x:row>
     <x:row r="48" ht="42" customHeight="1">
       <x:c r="A48" s="10" t="str">
-        <x:v>ISS-G01/G19/G20</x:v>
+        <x:v>SCH-T032-DUE14</x:v>
       </x:c>
       <x:c r="B48" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
-      </x:c>
-      <x:c r="C48" s="22" t="str">
-        <x:v>重大</x:v>
+        <x:v>进度资源Agent</x:v>
+      </x:c>
+      <x:c r="C48" s="23" t="str">
+        <x:v>高</x:v>
       </x:c>
       <x:c r="D48" s="10" t="str">
-        <x:v>G01/G19/G20</x:v>
+        <x:v>T032</x:v>
       </x:c>
       <x:c r="E48" s="10" t="str">
-        <x:v>未关闭问题</x:v>
+        <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F48" s="18" t="str">
-        <x:v>【连续第10期出现】项目章程和整体管理计划未正式批准：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第11期出现】汇总问题清单、适配结论和产品选型建议将在2026-09-25到期，当前状态为未开始。</x:v>
       </x:c>
       <x:c r="G48" s="18" t="str">
-        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+        <x:v>确认交付物、验收人和按期完成证据。</x:v>
       </x:c>
       <x:c r="H48" s="10" t="str">
-        <x:v>项目集经理</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="I48" s="10" t="str">
         <x:v>否</x:v>
@@ -2615,7 +2615,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K48" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L48" s="10" t="str"/>
       <x:c r="M48" s="21" t="str">
@@ -2625,28 +2625,28 @@
     </x:row>
     <x:row r="49" ht="42" customHeight="1">
       <x:c r="A49" s="10" t="str">
-        <x:v>ISS-G17</x:v>
+        <x:v>SCH-T033-DUE14</x:v>
       </x:c>
       <x:c r="B49" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
-      </x:c>
-      <x:c r="C49" s="22" t="str">
-        <x:v>重大</x:v>
+        <x:v>进度资源Agent</x:v>
+      </x:c>
+      <x:c r="C49" s="23" t="str">
+        <x:v>高</x:v>
       </x:c>
       <x:c r="D49" s="10" t="str">
-        <x:v>G17</x:v>
+        <x:v>T033</x:v>
       </x:c>
       <x:c r="E49" s="10" t="str">
-        <x:v>未关闭问题</x:v>
+        <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F49" s="18" t="str">
-        <x:v>【连续第10期出现】开发测试环境和配置管理未就绪：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第11期出现】编制并审批项目章程将在2026-10-02到期，当前状态为未开始。</x:v>
       </x:c>
       <x:c r="G49" s="18" t="str">
-        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+        <x:v>确认交付物、验收人和按期完成证据。</x:v>
       </x:c>
       <x:c r="H49" s="10" t="str">
-        <x:v>配置人员</x:v>
+        <x:v>项目集经理</x:v>
       </x:c>
       <x:c r="I49" s="10" t="str">
         <x:v>否</x:v>
@@ -2655,7 +2655,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K49" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L49" s="10" t="str"/>
       <x:c r="M49" s="21" t="str">
@@ -2665,28 +2665,28 @@
     </x:row>
     <x:row r="50" ht="42" customHeight="1">
       <x:c r="A50" s="10" t="str">
-        <x:v>ISS-G05</x:v>
+        <x:v>SCH-T034-DUE14</x:v>
       </x:c>
       <x:c r="B50" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
-      </x:c>
-      <x:c r="C50" s="22" t="str">
-        <x:v>重大</x:v>
+        <x:v>进度资源Agent</x:v>
+      </x:c>
+      <x:c r="C50" s="23" t="str">
+        <x:v>高</x:v>
       </x:c>
       <x:c r="D50" s="10" t="str">
-        <x:v>G05</x:v>
+        <x:v>T034</x:v>
       </x:c>
       <x:c r="E50" s="10" t="str">
-        <x:v>未关闭问题</x:v>
+        <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F50" s="18" t="str">
-        <x:v>【连续第10期出现】预算与成本控制口径未批准：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第5期出现】编制范围、里程碑和主进度计划将在2026-10-05到期，当前状态为未开始。</x:v>
       </x:c>
       <x:c r="G50" s="18" t="str">
-        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+        <x:v>确认交付物、验收人和按期完成证据。</x:v>
       </x:c>
       <x:c r="H50" s="10" t="str">
-        <x:v>项目集经理</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="I50" s="10" t="str">
         <x:v>否</x:v>
@@ -2695,7 +2695,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K50" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L50" s="10" t="str"/>
       <x:c r="M50" s="21" t="str">
@@ -2705,25 +2705,25 @@
     </x:row>
     <x:row r="51" ht="42" customHeight="1">
       <x:c r="A51" s="10" t="str">
-        <x:v>ISS-G07</x:v>
+        <x:v>SCH-T035-DUE14</x:v>
       </x:c>
       <x:c r="B51" s="10" t="str">
-        <x:v>风险问题Agent</x:v>
-      </x:c>
-      <x:c r="C51" s="22" t="str">
-        <x:v>重大</x:v>
+        <x:v>进度资源Agent</x:v>
+      </x:c>
+      <x:c r="C51" s="23" t="str">
+        <x:v>高</x:v>
       </x:c>
       <x:c r="D51" s="10" t="str">
-        <x:v>G07</x:v>
+        <x:v>T035</x:v>
       </x:c>
       <x:c r="E51" s="10" t="str">
-        <x:v>未关闭问题</x:v>
+        <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F51" s="18" t="str">
-        <x:v>【连续第10期出现】关键相关方对目标、范围和职责认知不一致：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第4期出现】建立项目组织、RACI与沟通机制将在2026-10-08到期，当前状态为未开始。</x:v>
       </x:c>
       <x:c r="G51" s="18" t="str">
-        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+        <x:v>确认交付物、验收人和按期完成证据。</x:v>
       </x:c>
       <x:c r="H51" s="10" t="str">
         <x:v>项目经理</x:v>
@@ -2735,7 +2735,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K51" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L51" s="10" t="str"/>
       <x:c r="M51" s="21" t="str">
@@ -2745,7 +2745,7 @@
     </x:row>
     <x:row r="52" ht="42" customHeight="1">
       <x:c r="A52" s="10" t="str">
-        <x:v>DEC-D-001</x:v>
+        <x:v>RSK-RSK-001</x:v>
       </x:c>
       <x:c r="B52" s="10" t="str">
         <x:v>风险问题Agent</x:v>
@@ -2754,28 +2754,28 @@
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D52" s="10" t="str">
-        <x:v>D-001</x:v>
+        <x:v>RSK-001</x:v>
       </x:c>
       <x:c r="E52" s="10" t="str">
-        <x:v>决策事项7天内到期</x:v>
+        <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F52" s="18" t="str">
-        <x:v>【连续第10期出现】CA、电子文档、BI产品选型（需要日期2026-09-25）</x:v>
+        <x:v>【连续第11期出现】CA、电子文档、BI产品POC与选型未按期完成</x:v>
       </x:c>
       <x:c r="G52" s="18" t="str">
-        <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
+        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
       </x:c>
       <x:c r="H52" s="10" t="str">
-        <x:v>项目指导委员会</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="I52" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J52" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K52" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L52" s="10" t="str"/>
       <x:c r="M52" s="21" t="str">
@@ -2785,7 +2785,7 @@
     </x:row>
     <x:row r="53" ht="42" customHeight="1">
       <x:c r="A53" s="10" t="str">
-        <x:v>DEC-D-002</x:v>
+        <x:v>RSK-RSK-002</x:v>
       </x:c>
       <x:c r="B53" s="10" t="str">
         <x:v>风险问题Agent</x:v>
@@ -2794,28 +2794,28 @@
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D53" s="10" t="str">
-        <x:v>D-002</x:v>
+        <x:v>RSK-002</x:v>
       </x:c>
       <x:c r="E53" s="10" t="str">
-        <x:v>待决策事项</x:v>
+        <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F53" s="18" t="str">
-        <x:v>【连续第10期出现】一期范围与P0需求基线（需要日期2026-10-09）</x:v>
+        <x:v>【连续第11期出现】总体技术架构基线未通过评审</x:v>
       </x:c>
       <x:c r="G53" s="18" t="str">
-        <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
+        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
       </x:c>
       <x:c r="H53" s="10" t="str">
-        <x:v>业务负责人/项目发起人</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="I53" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J53" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K53" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L53" s="10" t="str"/>
       <x:c r="M53" s="21" t="str">
@@ -2825,7 +2825,7 @@
     </x:row>
     <x:row r="54" ht="42" customHeight="1">
       <x:c r="A54" s="10" t="str">
-        <x:v>DEC-D-003</x:v>
+        <x:v>RSK-RSK-003</x:v>
       </x:c>
       <x:c r="B54" s="10" t="str">
         <x:v>风险问题Agent</x:v>
@@ -2834,28 +2834,28 @@
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D54" s="10" t="str">
-        <x:v>D-003</x:v>
+        <x:v>RSK-003</x:v>
       </x:c>
       <x:c r="E54" s="10" t="str">
-        <x:v>待决策事项</x:v>
+        <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F54" s="18" t="str">
-        <x:v>【连续第10期出现】项目预算与采购路径（需要日期2026-10-08）</x:v>
+        <x:v>【连续第11期出现】外部系统接口边界与联调窗口不明确</x:v>
       </x:c>
       <x:c r="G54" s="18" t="str">
-        <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
+        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
       </x:c>
       <x:c r="H54" s="10" t="str">
-        <x:v>项目发起人</x:v>
+        <x:v>项目经理</x:v>
       </x:c>
       <x:c r="I54" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J54" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K54" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L54" s="10" t="str"/>
       <x:c r="M54" s="21" t="str">
@@ -2865,7 +2865,7 @@
     </x:row>
     <x:row r="55" ht="42" customHeight="1">
       <x:c r="A55" s="10" t="str">
-        <x:v>DEC-D-004</x:v>
+        <x:v>RSK-RSK-004</x:v>
       </x:c>
       <x:c r="B55" s="10" t="str">
         <x:v>风险问题Agent</x:v>
@@ -2874,19 +2874,19 @@
         <x:v>重大</x:v>
       </x:c>
       <x:c r="D55" s="10" t="str">
-        <x:v>D-004</x:v>
+        <x:v>RSK-004</x:v>
       </x:c>
       <x:c r="E55" s="10" t="str">
-        <x:v>待决策事项</x:v>
+        <x:v>重大剩余风险</x:v>
       </x:c>
       <x:c r="F55" s="18" t="str">
-        <x:v>【连续第10期出现】2026年10月20日正式启动决策（需要日期2026-10-16）</x:v>
+        <x:v>【连续第11期出现】安全合规基线未形成或外部产品不满足要求</x:v>
       </x:c>
       <x:c r="G55" s="18" t="str">
-        <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
+        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
       </x:c>
       <x:c r="H55" s="10" t="str">
-        <x:v>项目指导委员会</x:v>
+        <x:v>技术经理</x:v>
       </x:c>
       <x:c r="I55" s="10" t="str">
         <x:v>是</x:v>
@@ -2895,7 +2895,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K55" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L55" s="10" t="str"/>
       <x:c r="M55" s="21" t="str">
@@ -2905,37 +2905,37 @@
     </x:row>
     <x:row r="56" ht="42" customHeight="1">
       <x:c r="A56" s="10" t="str">
-        <x:v>COM-DECISION-DEC-001</x:v>
+        <x:v>RSK-RSK-005</x:v>
       </x:c>
       <x:c r="B56" s="10" t="str">
-        <x:v>沟通报告Agent</x:v>
-      </x:c>
-      <x:c r="C56" s="23" t="str">
-        <x:v>高</x:v>
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C56" s="22" t="str">
+        <x:v>重大</x:v>
       </x:c>
       <x:c r="D56" s="10" t="str">
-        <x:v>DEC-001</x:v>
+        <x:v>RSK-005</x:v>
       </x:c>
       <x:c r="E56" s="10" t="str">
-        <x:v>决策事项14天内到期</x:v>
+        <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F56" s="18" t="str">
-        <x:v>【连续第5期出现】CA产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
+        <x:v>【连续第11期出现】30人团队未按阶段计划到位</x:v>
       </x:c>
       <x:c r="G56" s="18" t="str">
-        <x:v>将事实、备选方案、影响、建议和所需授权统一提交决策人。</x:v>
+        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
       </x:c>
       <x:c r="H56" s="10" t="str">
-        <x:v>项目治理委员会</x:v>
+        <x:v>项目集经理</x:v>
       </x:c>
       <x:c r="I56" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J56" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K56" s="10" t="n">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L56" s="10" t="str"/>
       <x:c r="M56" s="21" t="str">
@@ -2945,37 +2945,37 @@
     </x:row>
     <x:row r="57" ht="42" customHeight="1">
       <x:c r="A57" s="10" t="str">
-        <x:v>COM-DECISION-DEC-002</x:v>
+        <x:v>RSK-RSK-006</x:v>
       </x:c>
       <x:c r="B57" s="10" t="str">
-        <x:v>沟通报告Agent</x:v>
-      </x:c>
-      <x:c r="C57" s="23" t="str">
-        <x:v>高</x:v>
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C57" s="22" t="str">
+        <x:v>重大</x:v>
       </x:c>
       <x:c r="D57" s="10" t="str">
-        <x:v>DEC-002</x:v>
+        <x:v>RSK-006</x:v>
       </x:c>
       <x:c r="E57" s="10" t="str">
-        <x:v>决策事项14天内到期</x:v>
+        <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F57" s="18" t="str">
-        <x:v>【连续第5期出现】电子文档产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
+        <x:v>【连续第11期出现】一期范围与需求基线未确认</x:v>
       </x:c>
       <x:c r="G57" s="18" t="str">
-        <x:v>将事实、备选方案、影响、建议和所需授权统一提交决策人。</x:v>
+        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
       </x:c>
       <x:c r="H57" s="10" t="str">
-        <x:v>项目治理委员会</x:v>
+        <x:v>产品经理</x:v>
       </x:c>
       <x:c r="I57" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J57" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K57" s="10" t="n">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L57" s="10" t="str"/>
       <x:c r="M57" s="21" t="str">
@@ -2985,43 +2985,883 @@
     </x:row>
     <x:row r="58" ht="42" customHeight="1">
       <x:c r="A58" s="10" t="str">
-        <x:v>COM-DECISION-DEC-003</x:v>
+        <x:v>RSK-RSK-007</x:v>
       </x:c>
       <x:c r="B58" s="10" t="str">
-        <x:v>沟通报告Agent</x:v>
-      </x:c>
-      <x:c r="C58" s="23" t="str">
-        <x:v>高</x:v>
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C58" s="22" t="str">
+        <x:v>重大</x:v>
       </x:c>
       <x:c r="D58" s="10" t="str">
-        <x:v>DEC-003</x:v>
+        <x:v>RSK-007</x:v>
       </x:c>
       <x:c r="E58" s="10" t="str">
-        <x:v>决策事项14天内到期</x:v>
+        <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F58" s="18" t="str">
-        <x:v>【连续第5期出现】BI报表产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
+        <x:v>【连续第11期出现】历史合同数据质量不足或迁移范围失控</x:v>
       </x:c>
       <x:c r="G58" s="18" t="str">
-        <x:v>将事实、备选方案、影响、建议和所需授权统一提交决策人。</x:v>
+        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
       </x:c>
       <x:c r="H58" s="10" t="str">
-        <x:v>项目治理委员会</x:v>
+        <x:v>产品经理</x:v>
       </x:c>
       <x:c r="I58" s="10" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="J58" s="20" t="n">
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K58" s="10" t="n">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L58" s="10" t="str"/>
       <x:c r="M58" s="21" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="N58" s="21" t="str"/>
+    </x:row>
+    <x:row r="59" ht="42" customHeight="1">
+      <x:c r="A59" s="10" t="str">
+        <x:v>RSK-RSK-008</x:v>
+      </x:c>
+      <x:c r="B59" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C59" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D59" s="10" t="str">
+        <x:v>RSK-008</x:v>
+      </x:c>
+      <x:c r="E59" s="10" t="str">
+        <x:v>高剩余风险</x:v>
+      </x:c>
+      <x:c r="F59" s="18" t="str">
+        <x:v>【连续第11期出现】外部产品采购与合同条款不能支撑项目计划</x:v>
+      </x:c>
+      <x:c r="G59" s="18" t="str">
+        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
+      </x:c>
+      <x:c r="H59" s="10" t="str">
+        <x:v>项目集经理</x:v>
+      </x:c>
+      <x:c r="I59" s="10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J59" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K59" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L59" s="10" t="str"/>
+      <x:c r="M59" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N59" s="21" t="str"/>
+    </x:row>
+    <x:row r="60" ht="42" customHeight="1">
+      <x:c r="A60" s="10" t="str">
+        <x:v>RSK-RSK-009</x:v>
+      </x:c>
+      <x:c r="B60" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C60" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D60" s="10" t="str">
+        <x:v>RSK-009</x:v>
+      </x:c>
+      <x:c r="E60" s="10" t="str">
+        <x:v>高剩余风险</x:v>
+      </x:c>
+      <x:c r="F60" s="18" t="str">
+        <x:v>【连续第11期出现】项目章程和整体管理计划未正式批准</x:v>
+      </x:c>
+      <x:c r="G60" s="18" t="str">
+        <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
+      </x:c>
+      <x:c r="H60" s="10" t="str">
+        <x:v>项目集经理</x:v>
+      </x:c>
+      <x:c r="I60" s="10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J60" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K60" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L60" s="10" t="str"/>
+      <x:c r="M60" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N60" s="21" t="str"/>
+    </x:row>
+    <x:row r="61" ht="42" customHeight="1">
+      <x:c r="A61" s="10" t="str">
+        <x:v>ISS-G10</x:v>
+      </x:c>
+      <x:c r="B61" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C61" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D61" s="10" t="str">
+        <x:v>G10</x:v>
+      </x:c>
+      <x:c r="E61" s="10" t="str">
+        <x:v>未关闭问题</x:v>
+      </x:c>
+      <x:c r="F61" s="18" t="str">
+        <x:v>【连续第11期出现】CA、电子文档、BI产品POC与选型未按期完成：需在正式启动前完成证据确认</x:v>
+      </x:c>
+      <x:c r="G61" s="18" t="str">
+        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+      </x:c>
+      <x:c r="H61" s="10" t="str">
+        <x:v>技术经理</x:v>
+      </x:c>
+      <x:c r="I61" s="10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J61" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K61" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L61" s="10" t="str"/>
+      <x:c r="M61" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N61" s="21" t="str"/>
+    </x:row>
+    <x:row r="62" ht="42" customHeight="1">
+      <x:c r="A62" s="10" t="str">
+        <x:v>ISS-G09</x:v>
+      </x:c>
+      <x:c r="B62" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C62" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D62" s="10" t="str">
+        <x:v>G09</x:v>
+      </x:c>
+      <x:c r="E62" s="10" t="str">
+        <x:v>未关闭问题</x:v>
+      </x:c>
+      <x:c r="F62" s="18" t="str">
+        <x:v>【连续第11期出现】总体技术架构基线未通过评审：需在正式启动前完成证据确认</x:v>
+      </x:c>
+      <x:c r="G62" s="18" t="str">
+        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+      </x:c>
+      <x:c r="H62" s="10" t="str">
+        <x:v>技术经理</x:v>
+      </x:c>
+      <x:c r="I62" s="10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J62" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K62" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L62" s="10" t="str"/>
+      <x:c r="M62" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N62" s="21" t="str"/>
+    </x:row>
+    <x:row r="63" ht="42" customHeight="1">
+      <x:c r="A63" s="10" t="str">
+        <x:v>ISS-G19</x:v>
+      </x:c>
+      <x:c r="B63" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C63" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D63" s="10" t="str">
+        <x:v>G19</x:v>
+      </x:c>
+      <x:c r="E63" s="10" t="str">
+        <x:v>未关闭问题</x:v>
+      </x:c>
+      <x:c r="F63" s="18" t="str">
+        <x:v>【连续第11期出现】外部系统接口边界与联调窗口不明确：需在正式启动前完成证据确认</x:v>
+      </x:c>
+      <x:c r="G63" s="18" t="str">
+        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+      </x:c>
+      <x:c r="H63" s="10" t="str">
+        <x:v>项目经理</x:v>
+      </x:c>
+      <x:c r="I63" s="10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J63" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K63" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L63" s="10" t="str"/>
+      <x:c r="M63" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N63" s="21" t="str"/>
+    </x:row>
+    <x:row r="64" ht="42" customHeight="1">
+      <x:c r="A64" s="10" t="str">
+        <x:v>ISS-G16</x:v>
+      </x:c>
+      <x:c r="B64" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C64" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D64" s="10" t="str">
+        <x:v>G16</x:v>
+      </x:c>
+      <x:c r="E64" s="10" t="str">
+        <x:v>未关闭问题</x:v>
+      </x:c>
+      <x:c r="F64" s="18" t="str">
+        <x:v>【连续第11期出现】安全合规基线未形成或外部产品不满足要求：需在正式启动前完成证据确认</x:v>
+      </x:c>
+      <x:c r="G64" s="18" t="str">
+        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+      </x:c>
+      <x:c r="H64" s="10" t="str">
+        <x:v>技术经理</x:v>
+      </x:c>
+      <x:c r="I64" s="10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J64" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K64" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L64" s="10" t="str"/>
+      <x:c r="M64" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N64" s="21" t="str"/>
+    </x:row>
+    <x:row r="65" ht="42" customHeight="1">
+      <x:c r="A65" s="10" t="str">
+        <x:v>ISS-G08</x:v>
+      </x:c>
+      <x:c r="B65" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C65" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D65" s="10" t="str">
+        <x:v>G08</x:v>
+      </x:c>
+      <x:c r="E65" s="10" t="str">
+        <x:v>未关闭问题</x:v>
+      </x:c>
+      <x:c r="F65" s="18" t="str">
+        <x:v>【连续第11期出现】30人团队未按阶段计划到位：需在正式启动前完成证据确认</x:v>
+      </x:c>
+      <x:c r="G65" s="18" t="str">
+        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+      </x:c>
+      <x:c r="H65" s="10" t="str">
+        <x:v>项目集经理</x:v>
+      </x:c>
+      <x:c r="I65" s="10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J65" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K65" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L65" s="10" t="str"/>
+      <x:c r="M65" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N65" s="21" t="str"/>
+    </x:row>
+    <x:row r="66" ht="42" customHeight="1">
+      <x:c r="A66" s="10" t="str">
+        <x:v>ISS-G03/G11</x:v>
+      </x:c>
+      <x:c r="B66" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C66" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D66" s="10" t="str">
+        <x:v>G03/G11</x:v>
+      </x:c>
+      <x:c r="E66" s="10" t="str">
+        <x:v>未关闭问题</x:v>
+      </x:c>
+      <x:c r="F66" s="18" t="str">
+        <x:v>【连续第11期出现】一期范围与需求基线未确认：需在正式启动前完成证据确认</x:v>
+      </x:c>
+      <x:c r="G66" s="18" t="str">
+        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+      </x:c>
+      <x:c r="H66" s="10" t="str">
+        <x:v>产品经理</x:v>
+      </x:c>
+      <x:c r="I66" s="10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J66" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K66" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L66" s="10" t="str"/>
+      <x:c r="M66" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N66" s="21" t="str"/>
+    </x:row>
+    <x:row r="67" ht="42" customHeight="1">
+      <x:c r="A67" s="10" t="str">
+        <x:v>ISS-G15</x:v>
+      </x:c>
+      <x:c r="B67" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C67" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D67" s="10" t="str">
+        <x:v>G15</x:v>
+      </x:c>
+      <x:c r="E67" s="10" t="str">
+        <x:v>未关闭问题</x:v>
+      </x:c>
+      <x:c r="F67" s="18" t="str">
+        <x:v>【连续第11期出现】历史合同数据质量不足或迁移范围失控：需在正式启动前完成证据确认</x:v>
+      </x:c>
+      <x:c r="G67" s="18" t="str">
+        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+      </x:c>
+      <x:c r="H67" s="10" t="str">
+        <x:v>产品经理</x:v>
+      </x:c>
+      <x:c r="I67" s="10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J67" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K67" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L67" s="10" t="str"/>
+      <x:c r="M67" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N67" s="21" t="str"/>
+    </x:row>
+    <x:row r="68" ht="42" customHeight="1">
+      <x:c r="A68" s="10" t="str">
+        <x:v>ISS-G14</x:v>
+      </x:c>
+      <x:c r="B68" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C68" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D68" s="10" t="str">
+        <x:v>G14</x:v>
+      </x:c>
+      <x:c r="E68" s="10" t="str">
+        <x:v>未关闭问题</x:v>
+      </x:c>
+      <x:c r="F68" s="18" t="str">
+        <x:v>【连续第11期出现】外部产品采购与合同条款不能支撑项目计划：需在正式启动前完成证据确认</x:v>
+      </x:c>
+      <x:c r="G68" s="18" t="str">
+        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+      </x:c>
+      <x:c r="H68" s="10" t="str">
+        <x:v>项目集经理</x:v>
+      </x:c>
+      <x:c r="I68" s="10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J68" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K68" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L68" s="10" t="str"/>
+      <x:c r="M68" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N68" s="21" t="str"/>
+    </x:row>
+    <x:row r="69" ht="42" customHeight="1">
+      <x:c r="A69" s="10" t="str">
+        <x:v>ISS-G01/G19/G20</x:v>
+      </x:c>
+      <x:c r="B69" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C69" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D69" s="10" t="str">
+        <x:v>G01/G19/G20</x:v>
+      </x:c>
+      <x:c r="E69" s="10" t="str">
+        <x:v>未关闭问题</x:v>
+      </x:c>
+      <x:c r="F69" s="18" t="str">
+        <x:v>【连续第11期出现】项目章程和整体管理计划未正式批准：需在正式启动前完成证据确认</x:v>
+      </x:c>
+      <x:c r="G69" s="18" t="str">
+        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+      </x:c>
+      <x:c r="H69" s="10" t="str">
+        <x:v>项目集经理</x:v>
+      </x:c>
+      <x:c r="I69" s="10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J69" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K69" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L69" s="10" t="str"/>
+      <x:c r="M69" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N69" s="21" t="str"/>
+    </x:row>
+    <x:row r="70" ht="42" customHeight="1">
+      <x:c r="A70" s="10" t="str">
+        <x:v>ISS-G17</x:v>
+      </x:c>
+      <x:c r="B70" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C70" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D70" s="10" t="str">
+        <x:v>G17</x:v>
+      </x:c>
+      <x:c r="E70" s="10" t="str">
+        <x:v>未关闭问题</x:v>
+      </x:c>
+      <x:c r="F70" s="18" t="str">
+        <x:v>【连续第11期出现】开发测试环境和配置管理未就绪：需在正式启动前完成证据确认</x:v>
+      </x:c>
+      <x:c r="G70" s="18" t="str">
+        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+      </x:c>
+      <x:c r="H70" s="10" t="str">
+        <x:v>配置人员</x:v>
+      </x:c>
+      <x:c r="I70" s="10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J70" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K70" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L70" s="10" t="str"/>
+      <x:c r="M70" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N70" s="21" t="str"/>
+    </x:row>
+    <x:row r="71" ht="42" customHeight="1">
+      <x:c r="A71" s="10" t="str">
+        <x:v>ISS-G05</x:v>
+      </x:c>
+      <x:c r="B71" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C71" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D71" s="10" t="str">
+        <x:v>G05</x:v>
+      </x:c>
+      <x:c r="E71" s="10" t="str">
+        <x:v>未关闭问题</x:v>
+      </x:c>
+      <x:c r="F71" s="18" t="str">
+        <x:v>【连续第11期出现】预算与成本控制口径未批准：需在正式启动前完成证据确认</x:v>
+      </x:c>
+      <x:c r="G71" s="18" t="str">
+        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+      </x:c>
+      <x:c r="H71" s="10" t="str">
+        <x:v>项目集经理</x:v>
+      </x:c>
+      <x:c r="I71" s="10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J71" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K71" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L71" s="10" t="str"/>
+      <x:c r="M71" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N71" s="21" t="str"/>
+    </x:row>
+    <x:row r="72" ht="42" customHeight="1">
+      <x:c r="A72" s="10" t="str">
+        <x:v>ISS-G07</x:v>
+      </x:c>
+      <x:c r="B72" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C72" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D72" s="10" t="str">
+        <x:v>G07</x:v>
+      </x:c>
+      <x:c r="E72" s="10" t="str">
+        <x:v>未关闭问题</x:v>
+      </x:c>
+      <x:c r="F72" s="18" t="str">
+        <x:v>【连续第11期出现】关键相关方对目标、范围和职责认知不一致：需在正式启动前完成证据确认</x:v>
+      </x:c>
+      <x:c r="G72" s="18" t="str">
+        <x:v>确认根因、行动、期限和关闭证据。</x:v>
+      </x:c>
+      <x:c r="H72" s="10" t="str">
+        <x:v>项目经理</x:v>
+      </x:c>
+      <x:c r="I72" s="10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="J72" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K72" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L72" s="10" t="str"/>
+      <x:c r="M72" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N72" s="21" t="str"/>
+    </x:row>
+    <x:row r="73" ht="42" customHeight="1">
+      <x:c r="A73" s="10" t="str">
+        <x:v>DEC-D-001</x:v>
+      </x:c>
+      <x:c r="B73" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C73" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D73" s="10" t="str">
+        <x:v>D-001</x:v>
+      </x:c>
+      <x:c r="E73" s="10" t="str">
+        <x:v>决策事项7天内到期</x:v>
+      </x:c>
+      <x:c r="F73" s="18" t="str">
+        <x:v>【连续第11期出现】CA、电子文档、BI产品选型（需要日期2026-09-25）</x:v>
+      </x:c>
+      <x:c r="G73" s="18" t="str">
+        <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
+      </x:c>
+      <x:c r="H73" s="10" t="str">
+        <x:v>项目指导委员会</x:v>
+      </x:c>
+      <x:c r="I73" s="10" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="J73" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K73" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L73" s="10" t="str"/>
+      <x:c r="M73" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N73" s="21" t="str"/>
+    </x:row>
+    <x:row r="74" ht="42" customHeight="1">
+      <x:c r="A74" s="10" t="str">
+        <x:v>DEC-D-002</x:v>
+      </x:c>
+      <x:c r="B74" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C74" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D74" s="10" t="str">
+        <x:v>D-002</x:v>
+      </x:c>
+      <x:c r="E74" s="10" t="str">
+        <x:v>待决策事项</x:v>
+      </x:c>
+      <x:c r="F74" s="18" t="str">
+        <x:v>【连续第11期出现】一期范围与P0需求基线（需要日期2026-10-09）</x:v>
+      </x:c>
+      <x:c r="G74" s="18" t="str">
+        <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
+      </x:c>
+      <x:c r="H74" s="10" t="str">
+        <x:v>业务负责人/项目发起人</x:v>
+      </x:c>
+      <x:c r="I74" s="10" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="J74" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K74" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L74" s="10" t="str"/>
+      <x:c r="M74" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N74" s="21" t="str"/>
+    </x:row>
+    <x:row r="75" ht="42" customHeight="1">
+      <x:c r="A75" s="10" t="str">
+        <x:v>DEC-D-003</x:v>
+      </x:c>
+      <x:c r="B75" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C75" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D75" s="10" t="str">
+        <x:v>D-003</x:v>
+      </x:c>
+      <x:c r="E75" s="10" t="str">
+        <x:v>待决策事项</x:v>
+      </x:c>
+      <x:c r="F75" s="18" t="str">
+        <x:v>【连续第11期出现】项目预算与采购路径（需要日期2026-10-08）</x:v>
+      </x:c>
+      <x:c r="G75" s="18" t="str">
+        <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
+      </x:c>
+      <x:c r="H75" s="10" t="str">
+        <x:v>项目发起人</x:v>
+      </x:c>
+      <x:c r="I75" s="10" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="J75" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K75" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L75" s="10" t="str"/>
+      <x:c r="M75" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N75" s="21" t="str"/>
+    </x:row>
+    <x:row r="76" ht="42" customHeight="1">
+      <x:c r="A76" s="10" t="str">
+        <x:v>DEC-D-004</x:v>
+      </x:c>
+      <x:c r="B76" s="10" t="str">
+        <x:v>风险问题Agent</x:v>
+      </x:c>
+      <x:c r="C76" s="22" t="str">
+        <x:v>重大</x:v>
+      </x:c>
+      <x:c r="D76" s="10" t="str">
+        <x:v>D-004</x:v>
+      </x:c>
+      <x:c r="E76" s="10" t="str">
+        <x:v>待决策事项</x:v>
+      </x:c>
+      <x:c r="F76" s="18" t="str">
+        <x:v>【连续第11期出现】2026年10月20日正式启动决策（需要日期2026-10-16）</x:v>
+      </x:c>
+      <x:c r="G76" s="18" t="str">
+        <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
+      </x:c>
+      <x:c r="H76" s="10" t="str">
+        <x:v>项目指导委员会</x:v>
+      </x:c>
+      <x:c r="I76" s="10" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="J76" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K76" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L76" s="10" t="str"/>
+      <x:c r="M76" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N76" s="21" t="str"/>
+    </x:row>
+    <x:row r="77" ht="42" customHeight="1">
+      <x:c r="A77" s="10" t="str">
+        <x:v>COM-DECISION-DEC-001</x:v>
+      </x:c>
+      <x:c r="B77" s="10" t="str">
+        <x:v>沟通报告Agent</x:v>
+      </x:c>
+      <x:c r="C77" s="23" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="D77" s="10" t="str">
+        <x:v>DEC-001</x:v>
+      </x:c>
+      <x:c r="E77" s="10" t="str">
+        <x:v>决策事项14天内到期</x:v>
+      </x:c>
+      <x:c r="F77" s="18" t="str">
+        <x:v>【连续第6期出现】CA产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
+      </x:c>
+      <x:c r="G77" s="18" t="str">
+        <x:v>将事实、备选方案、影响、建议和所需授权统一提交决策人。</x:v>
+      </x:c>
+      <x:c r="H77" s="10" t="str">
+        <x:v>项目治理委员会</x:v>
+      </x:c>
+      <x:c r="I77" s="10" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="J77" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K77" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L77" s="10" t="str"/>
+      <x:c r="M77" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N77" s="21" t="str"/>
+    </x:row>
+    <x:row r="78" ht="42" customHeight="1">
+      <x:c r="A78" s="10" t="str">
+        <x:v>COM-DECISION-DEC-002</x:v>
+      </x:c>
+      <x:c r="B78" s="10" t="str">
+        <x:v>沟通报告Agent</x:v>
+      </x:c>
+      <x:c r="C78" s="23" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="D78" s="10" t="str">
+        <x:v>DEC-002</x:v>
+      </x:c>
+      <x:c r="E78" s="10" t="str">
+        <x:v>决策事项14天内到期</x:v>
+      </x:c>
+      <x:c r="F78" s="18" t="str">
+        <x:v>【连续第6期出现】电子文档产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
+      </x:c>
+      <x:c r="G78" s="18" t="str">
+        <x:v>将事实、备选方案、影响、建议和所需授权统一提交决策人。</x:v>
+      </x:c>
+      <x:c r="H78" s="10" t="str">
+        <x:v>项目治理委员会</x:v>
+      </x:c>
+      <x:c r="I78" s="10" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="J78" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K78" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L78" s="10" t="str"/>
+      <x:c r="M78" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N78" s="21" t="str"/>
+    </x:row>
+    <x:row r="79" ht="42" customHeight="1">
+      <x:c r="A79" s="10" t="str">
+        <x:v>COM-DECISION-DEC-003</x:v>
+      </x:c>
+      <x:c r="B79" s="10" t="str">
+        <x:v>沟通报告Agent</x:v>
+      </x:c>
+      <x:c r="C79" s="23" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="D79" s="10" t="str">
+        <x:v>DEC-003</x:v>
+      </x:c>
+      <x:c r="E79" s="10" t="str">
+        <x:v>决策事项14天内到期</x:v>
+      </x:c>
+      <x:c r="F79" s="18" t="str">
+        <x:v>【连续第6期出现】BI报表产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
+      </x:c>
+      <x:c r="G79" s="18" t="str">
+        <x:v>将事实、备选方案、影响、建议和所需授权统一提交决策人。</x:v>
+      </x:c>
+      <x:c r="H79" s="10" t="str">
+        <x:v>项目治理委员会</x:v>
+      </x:c>
+      <x:c r="I79" s="10" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="J79" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="K79" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L79" s="10" t="str"/>
+      <x:c r="M79" s="21" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="N79" s="21" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3029,7 +3869,7 @@
     <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="M5:M58">
+    <x:dataValidation type="list" sqref="M5:M79">
       <x:formula1>"待确认,已接受,需调整,已关闭"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -3094,7 +3934,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="str">
-        <x:v>SCH-T011-OVERDUE</x:v>
+        <x:v>SCH-T008-NORISK</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3103,15 +3943,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D6" s="10" t="str">
-        <x:v>T011</x:v>
+        <x:v>T008</x:v>
       </x:c>
       <x:c r="E6" s="10" t="n">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="str">
-        <x:v>SCH-T012-OVERDUE</x:v>
+        <x:v>SCH-T011-OVERDUE</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3120,15 +3960,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D7" s="10" t="str">
-        <x:v>T012</x:v>
+        <x:v>T011</x:v>
       </x:c>
       <x:c r="E7" s="10" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="str">
-        <x:v>SCH-T013-OVERDUE</x:v>
+        <x:v>SCH-T011-NORISK</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3137,15 +3977,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D8" s="10" t="str">
-        <x:v>T013</x:v>
+        <x:v>T011</x:v>
       </x:c>
       <x:c r="E8" s="10" t="n">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10" t="str">
-        <x:v>SCH-T014-OVERDUE</x:v>
+        <x:v>SCH-T012-OVERDUE</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3154,15 +3994,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D9" s="10" t="str">
-        <x:v>T014</x:v>
+        <x:v>T012</x:v>
       </x:c>
       <x:c r="E9" s="10" t="n">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="str">
-        <x:v>SCH-T015-OVERDUE</x:v>
+        <x:v>SCH-T012-NORISK</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3171,15 +4011,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D10" s="10" t="str">
-        <x:v>T015</x:v>
+        <x:v>T012</x:v>
       </x:c>
       <x:c r="E10" s="10" t="n">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="10" t="str">
-        <x:v>SCH-T016-OVERDUE</x:v>
+        <x:v>SCH-T013-OVERDUE</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3188,15 +4028,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D11" s="10" t="str">
-        <x:v>T016</x:v>
+        <x:v>T013</x:v>
       </x:c>
       <x:c r="E11" s="10" t="n">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="10" t="str">
-        <x:v>SCH-T017-OVERDUE</x:v>
+        <x:v>SCH-T013-NORISK</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3205,15 +4045,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D12" s="10" t="str">
-        <x:v>T017</x:v>
+        <x:v>T013</x:v>
       </x:c>
       <x:c r="E12" s="10" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="10" t="str">
-        <x:v>SCH-T018-OVERDUE</x:v>
+        <x:v>SCH-T014-OVERDUE</x:v>
       </x:c>
       <x:c r="B13" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3222,15 +4062,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D13" s="10" t="str">
-        <x:v>T018</x:v>
+        <x:v>T014</x:v>
       </x:c>
       <x:c r="E13" s="10" t="n">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="10" t="str">
-        <x:v>SCH-T019-OVERDUE</x:v>
+        <x:v>SCH-T014-NORISK</x:v>
       </x:c>
       <x:c r="B14" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3239,15 +4079,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D14" s="10" t="str">
-        <x:v>T019</x:v>
+        <x:v>T014</x:v>
       </x:c>
       <x:c r="E14" s="10" t="n">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="10" t="str">
-        <x:v>SCH-T020-OVERDUE</x:v>
+        <x:v>SCH-T015-OVERDUE</x:v>
       </x:c>
       <x:c r="B15" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3256,15 +4096,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D15" s="10" t="str">
-        <x:v>T020</x:v>
+        <x:v>T015</x:v>
       </x:c>
       <x:c r="E15" s="10" t="n">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="10" t="str">
-        <x:v>SCH-T021-OVERDUE</x:v>
+        <x:v>SCH-T015-NORISK</x:v>
       </x:c>
       <x:c r="B16" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3273,15 +4113,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D16" s="10" t="str">
-        <x:v>T021</x:v>
+        <x:v>T015</x:v>
       </x:c>
       <x:c r="E16" s="10" t="n">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="10" t="str">
-        <x:v>SCH-T022-OVERDUE</x:v>
+        <x:v>SCH-T016-OVERDUE</x:v>
       </x:c>
       <x:c r="B17" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3290,15 +4130,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D17" s="10" t="str">
-        <x:v>T022</x:v>
+        <x:v>T016</x:v>
       </x:c>
       <x:c r="E17" s="10" t="n">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="10" t="str">
-        <x:v>SCH-T023-OVERDUE</x:v>
+        <x:v>SCH-T016-NORISK</x:v>
       </x:c>
       <x:c r="B18" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3307,15 +4147,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D18" s="10" t="str">
-        <x:v>T023</x:v>
+        <x:v>T016</x:v>
       </x:c>
       <x:c r="E18" s="10" t="n">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="10" t="str">
-        <x:v>SCH-T024-DUE14</x:v>
+        <x:v>SCH-T017-OVERDUE</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3324,15 +4164,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D19" s="10" t="str">
-        <x:v>T024</x:v>
+        <x:v>T017</x:v>
       </x:c>
       <x:c r="E19" s="10" t="n">
-        <x:v>27</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="10" t="str">
-        <x:v>SCH-T025-OVERDUE</x:v>
+        <x:v>SCH-T017-NORISK</x:v>
       </x:c>
       <x:c r="B20" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3341,15 +4181,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D20" s="10" t="str">
-        <x:v>T025</x:v>
+        <x:v>T017</x:v>
       </x:c>
       <x:c r="E20" s="10" t="n">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="10" t="str">
-        <x:v>SCH-T026-OVERDUE</x:v>
+        <x:v>SCH-T018-OVERDUE</x:v>
       </x:c>
       <x:c r="B21" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3358,15 +4198,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D21" s="10" t="str">
-        <x:v>T026</x:v>
+        <x:v>T018</x:v>
       </x:c>
       <x:c r="E21" s="10" t="n">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="10" t="str">
-        <x:v>SCH-T027-OVERDUE</x:v>
+        <x:v>SCH-T018-NORISK</x:v>
       </x:c>
       <x:c r="B22" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3375,15 +4215,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D22" s="10" t="str">
-        <x:v>T027</x:v>
+        <x:v>T018</x:v>
       </x:c>
       <x:c r="E22" s="10" t="n">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="10" t="str">
-        <x:v>SCH-T028-OVERDUE</x:v>
+        <x:v>SCH-T019-OVERDUE</x:v>
       </x:c>
       <x:c r="B23" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3392,15 +4232,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D23" s="10" t="str">
-        <x:v>T028</x:v>
+        <x:v>T019</x:v>
       </x:c>
       <x:c r="E23" s="10" t="n">
-        <x:v>31</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="10" t="str">
-        <x:v>SCH-T029-OVERDUE</x:v>
+        <x:v>SCH-T019-NORISK</x:v>
       </x:c>
       <x:c r="B24" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3409,15 +4249,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D24" s="10" t="str">
-        <x:v>T029</x:v>
+        <x:v>T019</x:v>
       </x:c>
       <x:c r="E24" s="10" t="n">
-        <x:v>32</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="10" t="str">
-        <x:v>SCH-T030-OVERDUE</x:v>
+        <x:v>SCH-T020-OVERDUE</x:v>
       </x:c>
       <x:c r="B25" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3426,15 +4266,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D25" s="10" t="str">
-        <x:v>T030</x:v>
+        <x:v>T020</x:v>
       </x:c>
       <x:c r="E25" s="10" t="n">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="10" t="str">
-        <x:v>SCH-T031-OVERDUE</x:v>
+        <x:v>SCH-T020-NORISK</x:v>
       </x:c>
       <x:c r="B26" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3443,15 +4283,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D26" s="10" t="str">
-        <x:v>T031</x:v>
+        <x:v>T020</x:v>
       </x:c>
       <x:c r="E26" s="10" t="n">
-        <x:v>34</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="10" t="str">
-        <x:v>SCH-T032-DUE14</x:v>
+        <x:v>SCH-T021-OVERDUE</x:v>
       </x:c>
       <x:c r="B27" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3460,15 +4300,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D27" s="10" t="str">
-        <x:v>T032</x:v>
+        <x:v>T021</x:v>
       </x:c>
       <x:c r="E27" s="10" t="n">
-        <x:v>35</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="10" t="str">
-        <x:v>SCH-T033-DUE14</x:v>
+        <x:v>SCH-T021-NORISK</x:v>
       </x:c>
       <x:c r="B28" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3477,15 +4317,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D28" s="10" t="str">
-        <x:v>T033</x:v>
+        <x:v>T021</x:v>
       </x:c>
       <x:c r="E28" s="10" t="n">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="10" t="str">
-        <x:v>SCH-T034-DUE14</x:v>
+        <x:v>SCH-T022-OVERDUE</x:v>
       </x:c>
       <x:c r="B29" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3494,15 +4334,15 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D29" s="10" t="str">
-        <x:v>T034</x:v>
+        <x:v>T022</x:v>
       </x:c>
       <x:c r="E29" s="10" t="n">
-        <x:v>37</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="10" t="str">
-        <x:v>SCH-T035-DUE14</x:v>
+        <x:v>SCH-T022-NORISK</x:v>
       </x:c>
       <x:c r="B30" s="10" t="str">
         <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
@@ -3511,485 +4351,842 @@
         <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D30" s="10" t="str">
-        <x:v>T035</x:v>
+        <x:v>T022</x:v>
       </x:c>
       <x:c r="E30" s="10" t="n">
-        <x:v>38</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="10" t="str">
-        <x:v>RSK-RSK-001</x:v>
+        <x:v>SCH-T023-OVERDUE</x:v>
       </x:c>
       <x:c r="B31" s="10" t="str">
-        <x:v>风险管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C31" s="10" t="str">
-        <x:v>风险登记册</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D31" s="10" t="str">
-        <x:v>RSK-001</x:v>
+        <x:v>T023</x:v>
       </x:c>
       <x:c r="E31" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="10" t="str">
-        <x:v>RSK-RSK-002</x:v>
+        <x:v>SCH-T023-NORISK</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>风险管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C32" s="10" t="str">
-        <x:v>风险登记册</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D32" s="10" t="str">
-        <x:v>RSK-002</x:v>
+        <x:v>T023</x:v>
       </x:c>
       <x:c r="E32" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="10" t="str">
-        <x:v>RSK-RSK-003</x:v>
+        <x:v>SCH-T024-DUE14</x:v>
       </x:c>
       <x:c r="B33" s="10" t="str">
-        <x:v>风险管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C33" s="10" t="str">
-        <x:v>风险登记册</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D33" s="10" t="str">
-        <x:v>RSK-003</x:v>
+        <x:v>T024</x:v>
       </x:c>
       <x:c r="E33" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="10" t="str">
-        <x:v>RSK-RSK-004</x:v>
+        <x:v>SCH-T025-OVERDUE</x:v>
       </x:c>
       <x:c r="B34" s="10" t="str">
-        <x:v>风险管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C34" s="10" t="str">
-        <x:v>风险登记册</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D34" s="10" t="str">
-        <x:v>RSK-004</x:v>
+        <x:v>T025</x:v>
       </x:c>
       <x:c r="E34" s="10" t="n">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="10" t="str">
-        <x:v>RSK-RSK-005</x:v>
+        <x:v>SCH-T025-NORISK</x:v>
       </x:c>
       <x:c r="B35" s="10" t="str">
-        <x:v>风险管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C35" s="10" t="str">
-        <x:v>风险登记册</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D35" s="10" t="str">
-        <x:v>RSK-005</x:v>
+        <x:v>T025</x:v>
       </x:c>
       <x:c r="E35" s="10" t="n">
-        <x:v>13</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="10" t="str">
-        <x:v>RSK-RSK-006</x:v>
+        <x:v>SCH-T026-OVERDUE</x:v>
       </x:c>
       <x:c r="B36" s="10" t="str">
-        <x:v>风险管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C36" s="10" t="str">
-        <x:v>风险登记册</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D36" s="10" t="str">
-        <x:v>RSK-006</x:v>
+        <x:v>T026</x:v>
       </x:c>
       <x:c r="E36" s="10" t="n">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="10" t="str">
-        <x:v>RSK-RSK-007</x:v>
+        <x:v>SCH-T026-NORISK</x:v>
       </x:c>
       <x:c r="B37" s="10" t="str">
-        <x:v>风险管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C37" s="10" t="str">
-        <x:v>风险登记册</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D37" s="10" t="str">
-        <x:v>RSK-007</x:v>
+        <x:v>T026</x:v>
       </x:c>
       <x:c r="E37" s="10" t="n">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="10" t="str">
-        <x:v>RSK-RSK-008</x:v>
+        <x:v>SCH-T027-OVERDUE</x:v>
       </x:c>
       <x:c r="B38" s="10" t="str">
-        <x:v>风险管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C38" s="10" t="str">
-        <x:v>风险登记册</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D38" s="10" t="str">
-        <x:v>RSK-008</x:v>
+        <x:v>T027</x:v>
       </x:c>
       <x:c r="E38" s="10" t="n">
-        <x:v>16</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="10" t="str">
-        <x:v>RSK-RSK-009</x:v>
+        <x:v>SCH-T027-NORISK</x:v>
       </x:c>
       <x:c r="B39" s="10" t="str">
-        <x:v>风险管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C39" s="10" t="str">
-        <x:v>风险登记册</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D39" s="10" t="str">
-        <x:v>RSK-009</x:v>
+        <x:v>T027</x:v>
       </x:c>
       <x:c r="E39" s="10" t="n">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="10" t="str">
-        <x:v>ISS-G10</x:v>
+        <x:v>SCH-T028-OVERDUE</x:v>
       </x:c>
       <x:c r="B40" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C40" s="10" t="str">
-        <x:v>问题台账</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D40" s="10" t="str">
-        <x:v>G10</x:v>
+        <x:v>T028</x:v>
       </x:c>
       <x:c r="E40" s="10" t="n">
-        <x:v>4</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="10" t="str">
-        <x:v>ISS-G09</x:v>
+        <x:v>SCH-T028-NORISK</x:v>
       </x:c>
       <x:c r="B41" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C41" s="10" t="str">
-        <x:v>问题台账</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D41" s="10" t="str">
-        <x:v>G09</x:v>
+        <x:v>T028</x:v>
       </x:c>
       <x:c r="E41" s="10" t="n">
-        <x:v>5</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="10" t="str">
-        <x:v>ISS-G19</x:v>
+        <x:v>SCH-T029-OVERDUE</x:v>
       </x:c>
       <x:c r="B42" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C42" s="10" t="str">
-        <x:v>问题台账</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D42" s="10" t="str">
-        <x:v>G19</x:v>
+        <x:v>T029</x:v>
       </x:c>
       <x:c r="E42" s="10" t="n">
-        <x:v>6</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="10" t="str">
-        <x:v>ISS-G16</x:v>
+        <x:v>SCH-T029-NORISK</x:v>
       </x:c>
       <x:c r="B43" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C43" s="10" t="str">
-        <x:v>问题台账</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D43" s="10" t="str">
-        <x:v>G16</x:v>
+        <x:v>T029</x:v>
       </x:c>
       <x:c r="E43" s="10" t="n">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="10" t="str">
-        <x:v>ISS-G08</x:v>
+        <x:v>SCH-T030-OVERDUE</x:v>
       </x:c>
       <x:c r="B44" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C44" s="10" t="str">
-        <x:v>问题台账</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D44" s="10" t="str">
-        <x:v>G08</x:v>
+        <x:v>T030</x:v>
       </x:c>
       <x:c r="E44" s="10" t="n">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="10" t="str">
-        <x:v>ISS-G03/G11</x:v>
+        <x:v>SCH-T030-NORISK</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C45" s="10" t="str">
-        <x:v>问题台账</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D45" s="10" t="str">
-        <x:v>G03/G11</x:v>
+        <x:v>T030</x:v>
       </x:c>
       <x:c r="E45" s="10" t="n">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="10" t="str">
-        <x:v>ISS-G15</x:v>
+        <x:v>SCH-T031-OVERDUE</x:v>
       </x:c>
       <x:c r="B46" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C46" s="10" t="str">
-        <x:v>问题台账</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D46" s="10" t="str">
-        <x:v>G15</x:v>
+        <x:v>T031</x:v>
       </x:c>
       <x:c r="E46" s="10" t="n">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="10" t="str">
-        <x:v>ISS-G14</x:v>
+        <x:v>SCH-T031-NORISK</x:v>
       </x:c>
       <x:c r="B47" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C47" s="10" t="str">
-        <x:v>问题台账</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D47" s="10" t="str">
-        <x:v>G14</x:v>
+        <x:v>T031</x:v>
       </x:c>
       <x:c r="E47" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="10" t="str">
-        <x:v>ISS-G01/G19/G20</x:v>
+        <x:v>SCH-T032-DUE14</x:v>
       </x:c>
       <x:c r="B48" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C48" s="10" t="str">
-        <x:v>问题台账</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D48" s="10" t="str">
-        <x:v>G01/G19/G20</x:v>
+        <x:v>T032</x:v>
       </x:c>
       <x:c r="E48" s="10" t="n">
-        <x:v>12</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="10" t="str">
-        <x:v>ISS-G17</x:v>
+        <x:v>SCH-T033-DUE14</x:v>
       </x:c>
       <x:c r="B49" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C49" s="10" t="str">
-        <x:v>问题台账</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D49" s="10" t="str">
-        <x:v>G17</x:v>
+        <x:v>T033</x:v>
       </x:c>
       <x:c r="E49" s="10" t="n">
-        <x:v>13</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="10" t="str">
-        <x:v>ISS-G05</x:v>
+        <x:v>SCH-T034-DUE14</x:v>
       </x:c>
       <x:c r="B50" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C50" s="10" t="str">
-        <x:v>问题台账</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D50" s="10" t="str">
-        <x:v>G05</x:v>
+        <x:v>T034</x:v>
       </x:c>
       <x:c r="E50" s="10" t="n">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="10" t="str">
-        <x:v>ISS-G07</x:v>
+        <x:v>SCH-T035-DUE14</x:v>
       </x:c>
       <x:c r="B51" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>计划与进度管理-20260921-V1.xlsx</x:v>
       </x:c>
       <x:c r="C51" s="10" t="str">
-        <x:v>问题台账</x:v>
+        <x:v>项目总控台账</x:v>
       </x:c>
       <x:c r="D51" s="10" t="str">
-        <x:v>G07</x:v>
+        <x:v>T035</x:v>
       </x:c>
       <x:c r="E51" s="10" t="n">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="10" t="str">
-        <x:v>DEC-D-001</x:v>
+        <x:v>RSK-RSK-001</x:v>
       </x:c>
       <x:c r="B52" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>风险管理-20260918-V1.xlsx</x:v>
       </x:c>
       <x:c r="C52" s="10" t="str">
-        <x:v>待决策事项</x:v>
+        <x:v>风险登记册</x:v>
       </x:c>
       <x:c r="D52" s="10" t="str">
-        <x:v>D-001</x:v>
+        <x:v>RSK-001</x:v>
       </x:c>
       <x:c r="E52" s="10" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="10" t="str">
-        <x:v>DEC-D-002</x:v>
+        <x:v>RSK-RSK-002</x:v>
       </x:c>
       <x:c r="B53" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>风险管理-20260918-V1.xlsx</x:v>
       </x:c>
       <x:c r="C53" s="10" t="str">
-        <x:v>待决策事项</x:v>
+        <x:v>风险登记册</x:v>
       </x:c>
       <x:c r="D53" s="10" t="str">
-        <x:v>D-002</x:v>
+        <x:v>RSK-002</x:v>
       </x:c>
       <x:c r="E53" s="10" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="10" t="str">
-        <x:v>DEC-D-003</x:v>
+        <x:v>RSK-RSK-003</x:v>
       </x:c>
       <x:c r="B54" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>风险管理-20260918-V1.xlsx</x:v>
       </x:c>
       <x:c r="C54" s="10" t="str">
-        <x:v>待决策事项</x:v>
+        <x:v>风险登记册</x:v>
       </x:c>
       <x:c r="D54" s="10" t="str">
-        <x:v>D-003</x:v>
+        <x:v>RSK-003</x:v>
       </x:c>
       <x:c r="E54" s="10" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="10" t="str">
-        <x:v>DEC-D-004</x:v>
+        <x:v>RSK-RSK-004</x:v>
       </x:c>
       <x:c r="B55" s="10" t="str">
-        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+        <x:v>风险管理-20260918-V1.xlsx</x:v>
       </x:c>
       <x:c r="C55" s="10" t="str">
-        <x:v>待决策事项</x:v>
+        <x:v>风险登记册</x:v>
       </x:c>
       <x:c r="D55" s="10" t="str">
-        <x:v>D-004</x:v>
+        <x:v>RSK-004</x:v>
       </x:c>
       <x:c r="E55" s="10" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="10" t="str">
-        <x:v>COM-DECISION-DEC-001</x:v>
+        <x:v>RSK-RSK-005</x:v>
       </x:c>
       <x:c r="B56" s="10" t="str">
-        <x:v>沟通会议与报告-20260918-V3.xlsx</x:v>
+        <x:v>风险管理-20260918-V1.xlsx</x:v>
       </x:c>
       <x:c r="C56" s="10" t="str">
-        <x:v>决策日志</x:v>
+        <x:v>风险登记册</x:v>
       </x:c>
       <x:c r="D56" s="10" t="str">
-        <x:v>DEC-001</x:v>
+        <x:v>RSK-005</x:v>
       </x:c>
       <x:c r="E56" s="10" t="n">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="10" t="str">
-        <x:v>COM-DECISION-DEC-002</x:v>
+        <x:v>RSK-RSK-006</x:v>
       </x:c>
       <x:c r="B57" s="10" t="str">
-        <x:v>沟通会议与报告-20260918-V3.xlsx</x:v>
+        <x:v>风险管理-20260918-V1.xlsx</x:v>
       </x:c>
       <x:c r="C57" s="10" t="str">
-        <x:v>决策日志</x:v>
+        <x:v>风险登记册</x:v>
       </x:c>
       <x:c r="D57" s="10" t="str">
-        <x:v>DEC-002</x:v>
+        <x:v>RSK-006</x:v>
       </x:c>
       <x:c r="E57" s="10" t="n">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="10" t="str">
+        <x:v>RSK-RSK-007</x:v>
+      </x:c>
+      <x:c r="B58" s="10" t="str">
+        <x:v>风险管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C58" s="10" t="str">
+        <x:v>风险登记册</x:v>
+      </x:c>
+      <x:c r="D58" s="10" t="str">
+        <x:v>RSK-007</x:v>
+      </x:c>
+      <x:c r="E58" s="10" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="10" t="str">
+        <x:v>RSK-RSK-008</x:v>
+      </x:c>
+      <x:c r="B59" s="10" t="str">
+        <x:v>风险管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C59" s="10" t="str">
+        <x:v>风险登记册</x:v>
+      </x:c>
+      <x:c r="D59" s="10" t="str">
+        <x:v>RSK-008</x:v>
+      </x:c>
+      <x:c r="E59" s="10" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="10" t="str">
+        <x:v>RSK-RSK-009</x:v>
+      </x:c>
+      <x:c r="B60" s="10" t="str">
+        <x:v>风险管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C60" s="10" t="str">
+        <x:v>风险登记册</x:v>
+      </x:c>
+      <x:c r="D60" s="10" t="str">
+        <x:v>RSK-009</x:v>
+      </x:c>
+      <x:c r="E60" s="10" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="10" t="str">
+        <x:v>ISS-G10</x:v>
+      </x:c>
+      <x:c r="B61" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C61" s="10" t="str">
+        <x:v>问题台账</x:v>
+      </x:c>
+      <x:c r="D61" s="10" t="str">
+        <x:v>G10</x:v>
+      </x:c>
+      <x:c r="E61" s="10" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="10" t="str">
+        <x:v>ISS-G09</x:v>
+      </x:c>
+      <x:c r="B62" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C62" s="10" t="str">
+        <x:v>问题台账</x:v>
+      </x:c>
+      <x:c r="D62" s="10" t="str">
+        <x:v>G09</x:v>
+      </x:c>
+      <x:c r="E62" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="10" t="str">
+        <x:v>ISS-G19</x:v>
+      </x:c>
+      <x:c r="B63" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C63" s="10" t="str">
+        <x:v>问题台账</x:v>
+      </x:c>
+      <x:c r="D63" s="10" t="str">
+        <x:v>G19</x:v>
+      </x:c>
+      <x:c r="E63" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="10" t="str">
+        <x:v>ISS-G16</x:v>
+      </x:c>
+      <x:c r="B64" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C64" s="10" t="str">
+        <x:v>问题台账</x:v>
+      </x:c>
+      <x:c r="D64" s="10" t="str">
+        <x:v>G16</x:v>
+      </x:c>
+      <x:c r="E64" s="10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="10" t="str">
+        <x:v>ISS-G08</x:v>
+      </x:c>
+      <x:c r="B65" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C65" s="10" t="str">
+        <x:v>问题台账</x:v>
+      </x:c>
+      <x:c r="D65" s="10" t="str">
+        <x:v>G08</x:v>
+      </x:c>
+      <x:c r="E65" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="10" t="str">
+        <x:v>ISS-G03/G11</x:v>
+      </x:c>
+      <x:c r="B66" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C66" s="10" t="str">
+        <x:v>问题台账</x:v>
+      </x:c>
+      <x:c r="D66" s="10" t="str">
+        <x:v>G03/G11</x:v>
+      </x:c>
+      <x:c r="E66" s="10" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="10" t="str">
+        <x:v>ISS-G15</x:v>
+      </x:c>
+      <x:c r="B67" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C67" s="10" t="str">
+        <x:v>问题台账</x:v>
+      </x:c>
+      <x:c r="D67" s="10" t="str">
+        <x:v>G15</x:v>
+      </x:c>
+      <x:c r="E67" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="10" t="str">
+        <x:v>ISS-G14</x:v>
+      </x:c>
+      <x:c r="B68" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C68" s="10" t="str">
+        <x:v>问题台账</x:v>
+      </x:c>
+      <x:c r="D68" s="10" t="str">
+        <x:v>G14</x:v>
+      </x:c>
+      <x:c r="E68" s="10" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="10" t="str">
+        <x:v>ISS-G01/G19/G20</x:v>
+      </x:c>
+      <x:c r="B69" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C69" s="10" t="str">
+        <x:v>问题台账</x:v>
+      </x:c>
+      <x:c r="D69" s="10" t="str">
+        <x:v>G01/G19/G20</x:v>
+      </x:c>
+      <x:c r="E69" s="10" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="10" t="str">
+        <x:v>ISS-G17</x:v>
+      </x:c>
+      <x:c r="B70" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C70" s="10" t="str">
+        <x:v>问题台账</x:v>
+      </x:c>
+      <x:c r="D70" s="10" t="str">
+        <x:v>G17</x:v>
+      </x:c>
+      <x:c r="E70" s="10" t="n">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="10" t="str">
+        <x:v>ISS-G05</x:v>
+      </x:c>
+      <x:c r="B71" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C71" s="10" t="str">
+        <x:v>问题台账</x:v>
+      </x:c>
+      <x:c r="D71" s="10" t="str">
+        <x:v>G05</x:v>
+      </x:c>
+      <x:c r="E71" s="10" t="n">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="10" t="str">
+        <x:v>ISS-G07</x:v>
+      </x:c>
+      <x:c r="B72" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C72" s="10" t="str">
+        <x:v>问题台账</x:v>
+      </x:c>
+      <x:c r="D72" s="10" t="str">
+        <x:v>G07</x:v>
+      </x:c>
+      <x:c r="E72" s="10" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="10" t="str">
+        <x:v>DEC-D-001</x:v>
+      </x:c>
+      <x:c r="B73" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C73" s="10" t="str">
+        <x:v>待决策事项</x:v>
+      </x:c>
+      <x:c r="D73" s="10" t="str">
+        <x:v>D-001</x:v>
+      </x:c>
+      <x:c r="E73" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="10" t="str">
+        <x:v>DEC-D-002</x:v>
+      </x:c>
+      <x:c r="B74" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C74" s="10" t="str">
+        <x:v>待决策事项</x:v>
+      </x:c>
+      <x:c r="D74" s="10" t="str">
+        <x:v>D-002</x:v>
+      </x:c>
+      <x:c r="E74" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="10" t="str">
+        <x:v>DEC-D-003</x:v>
+      </x:c>
+      <x:c r="B75" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C75" s="10" t="str">
+        <x:v>待决策事项</x:v>
+      </x:c>
+      <x:c r="D75" s="10" t="str">
+        <x:v>D-003</x:v>
+      </x:c>
+      <x:c r="E75" s="10" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="10" t="str">
+        <x:v>DEC-D-004</x:v>
+      </x:c>
+      <x:c r="B76" s="10" t="str">
+        <x:v>问题与变更管理-20260918-V1.xlsx</x:v>
+      </x:c>
+      <x:c r="C76" s="10" t="str">
+        <x:v>待决策事项</x:v>
+      </x:c>
+      <x:c r="D76" s="10" t="str">
+        <x:v>D-004</x:v>
+      </x:c>
+      <x:c r="E76" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="10" t="str">
+        <x:v>COM-DECISION-DEC-001</x:v>
+      </x:c>
+      <x:c r="B77" s="10" t="str">
+        <x:v>沟通会议与报告-20260918-V3.xlsx</x:v>
+      </x:c>
+      <x:c r="C77" s="10" t="str">
+        <x:v>决策日志</x:v>
+      </x:c>
+      <x:c r="D77" s="10" t="str">
+        <x:v>DEC-001</x:v>
+      </x:c>
+      <x:c r="E77" s="10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="10" t="str">
+        <x:v>COM-DECISION-DEC-002</x:v>
+      </x:c>
+      <x:c r="B78" s="10" t="str">
+        <x:v>沟通会议与报告-20260918-V3.xlsx</x:v>
+      </x:c>
+      <x:c r="C78" s="10" t="str">
+        <x:v>决策日志</x:v>
+      </x:c>
+      <x:c r="D78" s="10" t="str">
+        <x:v>DEC-002</x:v>
+      </x:c>
+      <x:c r="E78" s="10" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="10" t="str">
         <x:v>COM-DECISION-DEC-003</x:v>
       </x:c>
-      <x:c r="B58" s="10" t="str">
+      <x:c r="B79" s="10" t="str">
         <x:v>沟通会议与报告-20260918-V3.xlsx</x:v>
       </x:c>
-      <x:c r="C58" s="10" t="str">
+      <x:c r="C79" s="10" t="str">
         <x:v>决策日志</x:v>
       </x:c>
-      <x:c r="D58" s="10" t="str">
+      <x:c r="D79" s="10" t="str">
         <x:v>DEC-003</x:v>
       </x:c>
-      <x:c r="E58" s="10" t="n">
+      <x:c r="E79" s="10" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -4044,7 +5241,7 @@
         <x:v>运行ID</x:v>
       </x:c>
       <x:c r="B7" s="18" t="str">
-        <x:v>AGENT-20260925-085337</x:v>
+        <x:v>AGENT-20260925-090621</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">

--- a/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO-Agent运行结果-20260925-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/11_AI_PMO中心/AI PMO-Agent运行结果-20260925-V1.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent总览" sheetId="1" r:id="R365e2b64bb3b4ba2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="管理层摘要" sheetId="2" r:id="R287972e717ab42b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发现清单" sheetId="3" r:id="Rdf58ee14b71c4ef8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据明细" sheetId="4" r:id="R0dd27842189a45d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="5" r:id="R058ff9b194ca42f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent总览" sheetId="1" r:id="R60a3cdf2b3e84c98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="管理层摘要" sheetId="2" r:id="R591c8ad14b254aed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发现清单" sheetId="3" r:id="R98c0edf1214a4764"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据明细" sheetId="4" r:id="R8fa205139c244b0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="5" r:id="Rad51fb80e9824d5e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -429,7 +429,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
-        <x:v>数据日期 2026-09-25｜运行ID AGENT-20260925-090621</x:v>
+        <x:v>数据日期 2026-09-25｜运行ID AGENT-20260925-102612</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
@@ -880,7 +880,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F5" s="18" t="str">
-        <x:v>【连续第5期出现】汇编可研报告并组织评审计划完成日为2026-09-18，当前状态为进行中。</x:v>
+        <x:v>【连续第6期出现】汇编可研报告并组织评审计划完成日为2026-09-18，当前状态为进行中。</x:v>
       </x:c>
       <x:c r="G5" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -895,7 +895,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K5" s="10" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L5" s="10" t="str"/>
       <x:c r="M5" s="21" t="str">
@@ -920,7 +920,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F6" s="18" t="str">
-        <x:v>汇编可研报告并组织评审（T008）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】汇编可研报告并组织评审（T008）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G6" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -935,7 +935,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K6" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L6" s="10" t="str"/>
       <x:c r="M6" s="21" t="str">
@@ -960,7 +960,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F7" s="18" t="str">
-        <x:v>【连续第11期出现】盘点既有系统、接口与数据计划完成日为2026-05-05，当前状态为进行中。</x:v>
+        <x:v>【连续第12期出现】盘点既有系统、接口与数据计划完成日为2026-05-05，当前状态为进行中。</x:v>
       </x:c>
       <x:c r="G7" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -975,7 +975,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K7" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L7" s="10" t="str"/>
       <x:c r="M7" s="21" t="str">
@@ -1000,7 +1000,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F8" s="18" t="str">
-        <x:v>盘点既有系统、接口与数据（T011）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】盘点既有系统、接口与数据（T011）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G8" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -1015,7 +1015,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K8" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L8" s="10" t="str"/>
       <x:c r="M8" s="21" t="str">
@@ -1040,7 +1040,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F9" s="18" t="str">
-        <x:v>【连续第11期出现】访谈业务部门并形成痛点清单计划完成日为2026-06-02，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】访谈业务部门并形成痛点清单计划完成日为2026-06-02，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G9" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1055,7 +1055,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K9" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L9" s="10" t="str"/>
       <x:c r="M9" s="21" t="str">
@@ -1080,7 +1080,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F10" s="18" t="str">
-        <x:v>访谈业务部门并形成痛点清单（T012）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】访谈业务部门并形成痛点清单（T012）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G10" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -1095,7 +1095,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K10" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L10" s="10" t="str"/>
       <x:c r="M10" s="21" t="str">
@@ -1120,7 +1120,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F11" s="18" t="str">
-        <x:v>【连续第11期出现】确认现状流程、问题与改进机会基线计划完成日为2026-06-30，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】确认现状流程、问题与改进机会基线计划完成日为2026-06-30，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G11" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1135,7 +1135,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K11" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L11" s="10" t="str"/>
       <x:c r="M11" s="21" t="str">
@@ -1160,7 +1160,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F12" s="18" t="str">
-        <x:v>确认现状流程、问题与改进机会基线（T013）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】确认现状流程、问题与改进机会基线（T013）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G12" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -1175,7 +1175,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K12" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L12" s="10" t="str"/>
       <x:c r="M12" s="21" t="str">
@@ -1200,7 +1200,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F13" s="18" t="str">
-        <x:v>【连续第11期出现】制定项目治理、会议与报告机制计划完成日为2026-07-12，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】制定项目治理、会议与报告机制计划完成日为2026-07-12，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G13" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1215,7 +1215,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K13" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L13" s="10" t="str"/>
       <x:c r="M13" s="21" t="str">
@@ -1240,7 +1240,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F14" s="18" t="str">
-        <x:v>制定项目治理、会议与报告机制（T014）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】制定项目治理、会议与报告机制（T014）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G14" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -1255,7 +1255,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K14" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L14" s="10" t="str"/>
       <x:c r="M14" s="21" t="str">
@@ -1280,7 +1280,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F15" s="18" t="str">
-        <x:v>【连续第11期出现】制定需求分级、跟踪与变更规范计划完成日为2026-07-24，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】制定需求分级、跟踪与变更规范计划完成日为2026-07-24，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G15" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1295,7 +1295,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K15" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L15" s="10" t="str"/>
       <x:c r="M15" s="21" t="str">
@@ -1320,7 +1320,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F16" s="18" t="str">
-        <x:v>制定需求分级、跟踪与变更规范（T015）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】制定需求分级、跟踪与变更规范（T015）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G16" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -1335,7 +1335,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K16" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L16" s="10" t="str"/>
       <x:c r="M16" s="21" t="str">
@@ -1360,7 +1360,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F17" s="18" t="str">
-        <x:v>【连续第11期出现】制定设计、编码与代码评审规范计划完成日为2026-08-06，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】制定设计、编码与代码评审规范计划完成日为2026-08-06，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G17" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1375,7 +1375,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K17" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L17" s="10" t="str"/>
       <x:c r="M17" s="21" t="str">
@@ -1400,7 +1400,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F18" s="18" t="str">
-        <x:v>制定设计、编码与代码评审规范（T016）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】制定设计、编码与代码评审规范（T016）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G18" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -1415,7 +1415,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K18" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L18" s="10" t="str"/>
       <x:c r="M18" s="21" t="str">
@@ -1440,7 +1440,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F19" s="18" t="str">
-        <x:v>【连续第11期出现】制定测试、缺陷与质量门禁规范计划完成日为2026-08-18，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】制定测试、缺陷与质量门禁规范计划完成日为2026-08-18，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G19" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1455,7 +1455,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K19" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L19" s="10" t="str"/>
       <x:c r="M19" s="21" t="str">
@@ -1480,7 +1480,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F20" s="18" t="str">
-        <x:v>制定测试、缺陷与质量门禁规范（T017）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】制定测试、缺陷与质量门禁规范（T017）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G20" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -1495,7 +1495,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K20" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L20" s="10" t="str"/>
       <x:c r="M20" s="21" t="str">
@@ -1520,7 +1520,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F21" s="18" t="str">
-        <x:v>【连续第11期出现】制定配置、发布与文档归档规范计划完成日为2026-08-31，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】制定配置、发布与文档归档规范计划完成日为2026-08-31，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G21" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1535,7 +1535,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K21" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L21" s="10" t="str"/>
       <x:c r="M21" s="21" t="str">
@@ -1560,7 +1560,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F22" s="18" t="str">
-        <x:v>制定配置、发布与文档归档规范（T018）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】制定配置、发布与文档归档规范（T018）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G22" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -1575,7 +1575,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K22" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L22" s="10" t="str"/>
       <x:c r="M22" s="21" t="str">
@@ -1600,7 +1600,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F23" s="18" t="str">
-        <x:v>【连续第11期出现】完成系统分层、模块与服务边界设计计划完成日为2026-07-15，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】完成系统分层、模块与服务边界设计计划完成日为2026-07-15，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G23" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1615,7 +1615,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K23" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L23" s="10" t="str"/>
       <x:c r="M23" s="21" t="str">
@@ -1640,7 +1640,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F24" s="18" t="str">
-        <x:v>完成系统分层、模块与服务边界设计（T019）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】完成系统分层、模块与服务边界设计（T019）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G24" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -1655,7 +1655,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K24" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L24" s="10" t="str"/>
       <x:c r="M24" s="21" t="str">
@@ -1680,7 +1680,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F25" s="18" t="str">
-        <x:v>【连续第11期出现】完成主数据、交易数据与分析数据架构计划完成日为2026-07-30，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】完成主数据、交易数据与分析数据架构计划完成日为2026-07-30，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G25" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1695,7 +1695,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K25" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L25" s="10" t="str"/>
       <x:c r="M25" s="21" t="str">
@@ -1720,7 +1720,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F26" s="18" t="str">
-        <x:v>完成主数据、交易数据与分析数据架构（T020）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】完成主数据、交易数据与分析数据架构（T020）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G26" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -1735,7 +1735,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K26" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L26" s="10" t="str"/>
       <x:c r="M26" s="21" t="str">
@@ -1760,7 +1760,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F27" s="18" t="str">
-        <x:v>【连续第11期出现】完成内部及外部接口总体架构计划完成日为2026-08-15，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】完成内部及外部接口总体架构计划完成日为2026-08-15，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G27" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1775,7 +1775,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K27" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L27" s="10" t="str"/>
       <x:c r="M27" s="21" t="str">
@@ -1800,7 +1800,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F28" s="18" t="str">
-        <x:v>完成内部及外部接口总体架构（T021）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】完成内部及外部接口总体架构（T021）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G28" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -1815,7 +1815,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K28" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L28" s="10" t="str"/>
       <x:c r="M28" s="21" t="str">
@@ -1840,7 +1840,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F29" s="18" t="str">
-        <x:v>【连续第11期出现】完成身份、权限、审计与数据安全设计计划完成日为2026-08-30，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】完成身份、权限、审计与数据安全设计计划完成日为2026-08-30，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G29" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1855,7 +1855,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K29" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L29" s="10" t="str"/>
       <x:c r="M29" s="21" t="str">
@@ -1880,7 +1880,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F30" s="18" t="str">
-        <x:v>完成身份、权限、审计与数据安全设计（T022）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】完成身份、权限、审计与数据安全设计（T022）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G30" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -1895,7 +1895,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K30" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L30" s="10" t="str"/>
       <x:c r="M30" s="21" t="str">
@@ -1920,7 +1920,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F31" s="18" t="str">
-        <x:v>【连续第11期出现】完成环境、网络、容灾和DevOps设计计划完成日为2026-09-14，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】完成环境、网络、容灾和DevOps设计计划完成日为2026-09-14，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G31" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -1935,7 +1935,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K31" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L31" s="10" t="str"/>
       <x:c r="M31" s="21" t="str">
@@ -1960,7 +1960,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F32" s="18" t="str">
-        <x:v>完成环境、网络、容灾和DevOps设计（T023）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】完成环境、网络、容灾和DevOps设计（T023）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G32" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -1975,7 +1975,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K32" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L32" s="10" t="str"/>
       <x:c r="M32" s="21" t="str">
@@ -2000,7 +2000,7 @@
         <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F33" s="18" t="str">
-        <x:v>【连续第11期出现】汇编总体技术架构并完成基线评审将在2026-09-30到期，当前状态为进行中。</x:v>
+        <x:v>【连续第12期出现】汇编总体技术架构并完成基线评审将在2026-09-30到期，当前状态为进行中。</x:v>
       </x:c>
       <x:c r="G33" s="18" t="str">
         <x:v>确认交付物、验收人和按期完成证据。</x:v>
@@ -2015,7 +2015,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K33" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L33" s="10" t="str"/>
       <x:c r="M33" s="21" t="str">
@@ -2040,7 +2040,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F34" s="18" t="str">
-        <x:v>【连续第11期出现】编制CA、电子文档、BI报表POC方案与评分标准计划完成日为2026-08-19，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】编制CA、电子文档、BI报表POC方案与评分标准计划完成日为2026-08-19，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G34" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -2055,7 +2055,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K34" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L34" s="10" t="str"/>
       <x:c r="M34" s="21" t="str">
@@ -2080,7 +2080,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F35" s="18" t="str">
-        <x:v>编制CA、电子文档、BI报表POC方案与评分标准（T025）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】编制CA、电子文档、BI报表POC方案与评分标准（T025）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G35" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -2095,7 +2095,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K35" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L35" s="10" t="str"/>
       <x:c r="M35" s="21" t="str">
@@ -2120,7 +2120,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F36" s="18" t="str">
-        <x:v>【连续第11期出现】验证证书签发、身份认证和证书管理计划完成日为2026-08-24，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】验证证书签发、身份认证和证书管理计划完成日为2026-08-24，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G36" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -2135,7 +2135,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K36" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L36" s="10" t="str"/>
       <x:c r="M36" s="21" t="str">
@@ -2160,7 +2160,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F37" s="18" t="str">
-        <x:v>验证证书签发、身份认证和证书管理（T026）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】验证证书签发、身份认证和证书管理（T026）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G37" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -2175,7 +2175,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K37" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L37" s="10" t="str"/>
       <x:c r="M37" s="21" t="str">
@@ -2200,7 +2200,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F38" s="18" t="str">
-        <x:v>【连续第11期出现】验证电子签名、验签、时间戳和审计追溯计划完成日为2026-08-29，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】验证电子签名、验签、时间戳和审计追溯计划完成日为2026-08-29，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G38" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -2215,7 +2215,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K38" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L38" s="10" t="str"/>
       <x:c r="M38" s="21" t="str">
@@ -2240,7 +2240,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F39" s="18" t="str">
-        <x:v>验证电子签名、验签、时间戳和审计追溯（T027）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】验证电子签名、验签、时间戳和审计追溯（T027）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G39" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -2255,7 +2255,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K39" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L39" s="10" t="str"/>
       <x:c r="M39" s="21" t="str">
@@ -2280,7 +2280,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F40" s="18" t="str">
-        <x:v>【连续第11期出现】验证模板生成、在线预览和格式转换计划完成日为2026-09-04，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】验证模板生成、在线预览和格式转换计划完成日为2026-09-04，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G40" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -2295,7 +2295,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K40" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L40" s="10" t="str"/>
       <x:c r="M40" s="21" t="str">
@@ -2320,7 +2320,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F41" s="18" t="str">
-        <x:v>验证模板生成、在线预览和格式转换（T028）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】验证模板生成、在线预览和格式转换（T028）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G41" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -2335,7 +2335,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K41" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L41" s="10" t="str"/>
       <x:c r="M41" s="21" t="str">
@@ -2360,7 +2360,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F42" s="18" t="str">
-        <x:v>【连续第11期出现】验证水印、权限控制、归档和大文件性能计划完成日为2026-09-09，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】验证水印、权限控制、归档和大文件性能计划完成日为2026-09-09，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G42" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -2375,7 +2375,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K42" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L42" s="10" t="str"/>
       <x:c r="M42" s="21" t="str">
@@ -2400,7 +2400,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F43" s="18" t="str">
-        <x:v>验证水印、权限控制、归档和大文件性能（T029）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】验证水印、权限控制、归档和大文件性能（T029）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G43" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -2415,7 +2415,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K43" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L43" s="10" t="str"/>
       <x:c r="M43" s="21" t="str">
@@ -2440,7 +2440,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F44" s="18" t="str">
-        <x:v>【连续第11期出现】验证数据接入、指标模型和经营报表计划完成日为2026-09-14，当前状态为待确认。</x:v>
+        <x:v>【连续第12期出现】验证数据接入、指标模型和经营报表计划完成日为2026-09-14，当前状态为待确认。</x:v>
       </x:c>
       <x:c r="G44" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -2455,7 +2455,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K44" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L44" s="10" t="str"/>
       <x:c r="M44" s="21" t="str">
@@ -2480,7 +2480,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F45" s="18" t="str">
-        <x:v>验证数据接入、指标模型和经营报表（T030）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】验证数据接入、指标模型和经营报表（T030）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G45" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -2495,7 +2495,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K45" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L45" s="10" t="str"/>
       <x:c r="M45" s="21" t="str">
@@ -2520,7 +2520,7 @@
         <x:v>任务已延期</x:v>
       </x:c>
       <x:c r="F46" s="18" t="str">
-        <x:v>【连续第5期出现】验证权限、钻取、导出和查询性能计划完成日为2026-09-19，当前状态为进行中。</x:v>
+        <x:v>【连续第6期出现】验证权限、钻取、导出和查询性能计划完成日为2026-09-19，当前状态为进行中。</x:v>
       </x:c>
       <x:c r="G46" s="18" t="str">
         <x:v>确认实际状态、纠偏计划、承诺日期和完成证据。</x:v>
@@ -2535,7 +2535,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K46" s="10" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L46" s="10" t="str"/>
       <x:c r="M46" s="21" t="str">
@@ -2560,7 +2560,7 @@
         <x:v>延期任务未关联风险登记</x:v>
       </x:c>
       <x:c r="F47" s="18" t="str">
-        <x:v>验证权限、钻取、导出和查询性能（T031）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
+        <x:v>【连续第2期出现】验证权限、钻取、导出和查询性能（T031）已延期，但风险登记册中未提及该任务编号，建议评估是否登记风险。</x:v>
       </x:c>
       <x:c r="G47" s="18" t="str">
         <x:v>结合延期原因评估是否新增风险条目并指定应对措施。</x:v>
@@ -2575,7 +2575,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K47" s="10" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L47" s="10" t="str"/>
       <x:c r="M47" s="21" t="str">
@@ -2600,7 +2600,7 @@
         <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F48" s="18" t="str">
-        <x:v>【连续第11期出现】汇总问题清单、适配结论和产品选型建议将在2026-09-25到期，当前状态为未开始。</x:v>
+        <x:v>【连续第12期出现】汇总问题清单、适配结论和产品选型建议将在2026-09-25到期，当前状态为未开始。</x:v>
       </x:c>
       <x:c r="G48" s="18" t="str">
         <x:v>确认交付物、验收人和按期完成证据。</x:v>
@@ -2615,7 +2615,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K48" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L48" s="10" t="str"/>
       <x:c r="M48" s="21" t="str">
@@ -2640,7 +2640,7 @@
         <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F49" s="18" t="str">
-        <x:v>【连续第11期出现】编制并审批项目章程将在2026-10-02到期，当前状态为未开始。</x:v>
+        <x:v>【连续第12期出现】编制并审批项目章程将在2026-10-02到期，当前状态为未开始。</x:v>
       </x:c>
       <x:c r="G49" s="18" t="str">
         <x:v>确认交付物、验收人和按期完成证据。</x:v>
@@ -2655,7 +2655,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K49" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L49" s="10" t="str"/>
       <x:c r="M49" s="21" t="str">
@@ -2680,7 +2680,7 @@
         <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F50" s="18" t="str">
-        <x:v>【连续第5期出现】编制范围、里程碑和主进度计划将在2026-10-05到期，当前状态为未开始。</x:v>
+        <x:v>【连续第6期出现】编制范围、里程碑和主进度计划将在2026-10-05到期，当前状态为未开始。</x:v>
       </x:c>
       <x:c r="G50" s="18" t="str">
         <x:v>确认交付物、验收人和按期完成证据。</x:v>
@@ -2695,7 +2695,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K50" s="10" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L50" s="10" t="str"/>
       <x:c r="M50" s="21" t="str">
@@ -2720,7 +2720,7 @@
         <x:v>任务14天内到期</x:v>
       </x:c>
       <x:c r="F51" s="18" t="str">
-        <x:v>【连续第4期出现】建立项目组织、RACI与沟通机制将在2026-10-08到期，当前状态为未开始。</x:v>
+        <x:v>【连续第5期出现】建立项目组织、RACI与沟通机制将在2026-10-08到期，当前状态为未开始。</x:v>
       </x:c>
       <x:c r="G51" s="18" t="str">
         <x:v>确认交付物、验收人和按期完成证据。</x:v>
@@ -2735,7 +2735,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K51" s="10" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L51" s="10" t="str"/>
       <x:c r="M51" s="21" t="str">
@@ -2760,7 +2760,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F52" s="18" t="str">
-        <x:v>【连续第11期出现】CA、电子文档、BI产品POC与选型未按期完成</x:v>
+        <x:v>【连续第12期出现】CA、电子文档、BI产品POC与选型未按期完成</x:v>
       </x:c>
       <x:c r="G52" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -2775,7 +2775,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K52" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L52" s="10" t="str"/>
       <x:c r="M52" s="21" t="str">
@@ -2800,7 +2800,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F53" s="18" t="str">
-        <x:v>【连续第11期出现】总体技术架构基线未通过评审</x:v>
+        <x:v>【连续第12期出现】总体技术架构基线未通过评审</x:v>
       </x:c>
       <x:c r="G53" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -2815,7 +2815,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K53" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L53" s="10" t="str"/>
       <x:c r="M53" s="21" t="str">
@@ -2840,7 +2840,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F54" s="18" t="str">
-        <x:v>【连续第11期出现】外部系统接口边界与联调窗口不明确</x:v>
+        <x:v>【连续第12期出现】外部系统接口边界与联调窗口不明确</x:v>
       </x:c>
       <x:c r="G54" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -2855,7 +2855,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K54" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L54" s="10" t="str"/>
       <x:c r="M54" s="21" t="str">
@@ -2880,7 +2880,7 @@
         <x:v>重大剩余风险</x:v>
       </x:c>
       <x:c r="F55" s="18" t="str">
-        <x:v>【连续第11期出现】安全合规基线未形成或外部产品不满足要求</x:v>
+        <x:v>【连续第12期出现】安全合规基线未形成或外部产品不满足要求</x:v>
       </x:c>
       <x:c r="G55" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -2895,7 +2895,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K55" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L55" s="10" t="str"/>
       <x:c r="M55" s="21" t="str">
@@ -2920,7 +2920,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F56" s="18" t="str">
-        <x:v>【连续第11期出现】30人团队未按阶段计划到位</x:v>
+        <x:v>【连续第12期出现】30人团队未按阶段计划到位</x:v>
       </x:c>
       <x:c r="G56" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -2935,7 +2935,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K56" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L56" s="10" t="str"/>
       <x:c r="M56" s="21" t="str">
@@ -2960,7 +2960,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F57" s="18" t="str">
-        <x:v>【连续第11期出现】一期范围与需求基线未确认</x:v>
+        <x:v>【连续第12期出现】一期范围与需求基线未确认</x:v>
       </x:c>
       <x:c r="G57" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -2975,7 +2975,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K57" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L57" s="10" t="str"/>
       <x:c r="M57" s="21" t="str">
@@ -3000,7 +3000,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F58" s="18" t="str">
-        <x:v>【连续第11期出现】历史合同数据质量不足或迁移范围失控</x:v>
+        <x:v>【连续第12期出现】历史合同数据质量不足或迁移范围失控</x:v>
       </x:c>
       <x:c r="G58" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -3015,7 +3015,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K58" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L58" s="10" t="str"/>
       <x:c r="M58" s="21" t="str">
@@ -3040,7 +3040,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F59" s="18" t="str">
-        <x:v>【连续第11期出现】外部产品采购与合同条款不能支撑项目计划</x:v>
+        <x:v>【连续第12期出现】外部产品采购与合同条款不能支撑项目计划</x:v>
       </x:c>
       <x:c r="G59" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -3055,7 +3055,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K59" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L59" s="10" t="str"/>
       <x:c r="M59" s="21" t="str">
@@ -3080,7 +3080,7 @@
         <x:v>高剩余风险</x:v>
       </x:c>
       <x:c r="F60" s="18" t="str">
-        <x:v>【连续第11期出现】项目章程和整体管理计划未正式批准</x:v>
+        <x:v>【连续第12期出现】项目章程和整体管理计划未正式批准</x:v>
       </x:c>
       <x:c r="G60" s="18" t="str">
         <x:v>复核触发条件、应对行动、剩余风险和升级结论。</x:v>
@@ -3095,7 +3095,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K60" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L60" s="10" t="str"/>
       <x:c r="M60" s="21" t="str">
@@ -3120,7 +3120,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F61" s="18" t="str">
-        <x:v>【连续第11期出现】CA、电子文档、BI产品POC与选型未按期完成：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第12期出现】CA、电子文档、BI产品POC与选型未按期完成：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G61" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -3135,7 +3135,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K61" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L61" s="10" t="str"/>
       <x:c r="M61" s="21" t="str">
@@ -3160,7 +3160,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F62" s="18" t="str">
-        <x:v>【连续第11期出现】总体技术架构基线未通过评审：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第12期出现】总体技术架构基线未通过评审：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G62" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -3175,7 +3175,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K62" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L62" s="10" t="str"/>
       <x:c r="M62" s="21" t="str">
@@ -3200,7 +3200,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F63" s="18" t="str">
-        <x:v>【连续第11期出现】外部系统接口边界与联调窗口不明确：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第12期出现】外部系统接口边界与联调窗口不明确：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G63" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -3215,7 +3215,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K63" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L63" s="10" t="str"/>
       <x:c r="M63" s="21" t="str">
@@ -3240,7 +3240,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F64" s="18" t="str">
-        <x:v>【连续第11期出现】安全合规基线未形成或外部产品不满足要求：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第12期出现】安全合规基线未形成或外部产品不满足要求：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G64" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -3255,7 +3255,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K64" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L64" s="10" t="str"/>
       <x:c r="M64" s="21" t="str">
@@ -3280,7 +3280,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F65" s="18" t="str">
-        <x:v>【连续第11期出现】30人团队未按阶段计划到位：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第12期出现】30人团队未按阶段计划到位：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G65" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -3295,7 +3295,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K65" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L65" s="10" t="str"/>
       <x:c r="M65" s="21" t="str">
@@ -3320,7 +3320,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F66" s="18" t="str">
-        <x:v>【连续第11期出现】一期范围与需求基线未确认：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第12期出现】一期范围与需求基线未确认：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G66" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -3335,7 +3335,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K66" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L66" s="10" t="str"/>
       <x:c r="M66" s="21" t="str">
@@ -3360,7 +3360,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F67" s="18" t="str">
-        <x:v>【连续第11期出现】历史合同数据质量不足或迁移范围失控：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第12期出现】历史合同数据质量不足或迁移范围失控：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G67" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -3375,7 +3375,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K67" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L67" s="10" t="str"/>
       <x:c r="M67" s="21" t="str">
@@ -3400,7 +3400,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F68" s="18" t="str">
-        <x:v>【连续第11期出现】外部产品采购与合同条款不能支撑项目计划：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第12期出现】外部产品采购与合同条款不能支撑项目计划：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G68" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -3415,7 +3415,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K68" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L68" s="10" t="str"/>
       <x:c r="M68" s="21" t="str">
@@ -3440,7 +3440,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F69" s="18" t="str">
-        <x:v>【连续第11期出现】项目章程和整体管理计划未正式批准：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第12期出现】项目章程和整体管理计划未正式批准：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G69" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -3455,7 +3455,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K69" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L69" s="10" t="str"/>
       <x:c r="M69" s="21" t="str">
@@ -3480,7 +3480,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F70" s="18" t="str">
-        <x:v>【连续第11期出现】开发测试环境和配置管理未就绪：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第12期出现】开发测试环境和配置管理未就绪：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G70" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -3495,7 +3495,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K70" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L70" s="10" t="str"/>
       <x:c r="M70" s="21" t="str">
@@ -3520,7 +3520,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F71" s="18" t="str">
-        <x:v>【连续第11期出现】预算与成本控制口径未批准：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第12期出现】预算与成本控制口径未批准：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G71" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -3535,7 +3535,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K71" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L71" s="10" t="str"/>
       <x:c r="M71" s="21" t="str">
@@ -3560,7 +3560,7 @@
         <x:v>未关闭问题</x:v>
       </x:c>
       <x:c r="F72" s="18" t="str">
-        <x:v>【连续第11期出现】关键相关方对目标、范围和职责认知不一致：需在正式启动前完成证据确认</x:v>
+        <x:v>【连续第12期出现】关键相关方对目标、范围和职责认知不一致：需在正式启动前完成证据确认</x:v>
       </x:c>
       <x:c r="G72" s="18" t="str">
         <x:v>确认根因、行动、期限和关闭证据。</x:v>
@@ -3575,7 +3575,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K72" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L72" s="10" t="str"/>
       <x:c r="M72" s="21" t="str">
@@ -3600,7 +3600,7 @@
         <x:v>决策事项7天内到期</x:v>
       </x:c>
       <x:c r="F73" s="18" t="str">
-        <x:v>【连续第11期出现】CA、电子文档、BI产品选型（需要日期2026-09-25）</x:v>
+        <x:v>【连续第12期出现】CA、电子文档、BI产品选型（需要日期2026-09-25）</x:v>
       </x:c>
       <x:c r="G73" s="18" t="str">
         <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
@@ -3615,7 +3615,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K73" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L73" s="10" t="str"/>
       <x:c r="M73" s="21" t="str">
@@ -3640,7 +3640,7 @@
         <x:v>待决策事项</x:v>
       </x:c>
       <x:c r="F74" s="18" t="str">
-        <x:v>【连续第11期出现】一期范围与P0需求基线（需要日期2026-10-09）</x:v>
+        <x:v>【连续第12期出现】一期范围与P0需求基线（需要日期2026-10-09）</x:v>
       </x:c>
       <x:c r="G74" s="18" t="str">
         <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
@@ -3655,7 +3655,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K74" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L74" s="10" t="str"/>
       <x:c r="M74" s="21" t="str">
@@ -3680,7 +3680,7 @@
         <x:v>待决策事项</x:v>
       </x:c>
       <x:c r="F75" s="18" t="str">
-        <x:v>【连续第11期出现】项目预算与采购路径（需要日期2026-10-08）</x:v>
+        <x:v>【连续第12期出现】项目预算与采购路径（需要日期2026-10-08）</x:v>
       </x:c>
       <x:c r="G75" s="18" t="str">
         <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
@@ -3695,7 +3695,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K75" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L75" s="10" t="str"/>
       <x:c r="M75" s="21" t="str">
@@ -3720,7 +3720,7 @@
         <x:v>待决策事项</x:v>
       </x:c>
       <x:c r="F76" s="18" t="str">
-        <x:v>【连续第11期出现】2026年10月20日正式启动决策（需要日期2026-10-16）</x:v>
+        <x:v>【连续第12期出现】2026年10月20日正式启动决策（需要日期2026-10-16）</x:v>
       </x:c>
       <x:c r="G76" s="18" t="str">
         <x:v>明确决策人、最迟日期、备选方案和延迟后果。</x:v>
@@ -3735,7 +3735,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K76" s="10" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L76" s="10" t="str"/>
       <x:c r="M76" s="21" t="str">
@@ -3760,7 +3760,7 @@
         <x:v>决策事项14天内到期</x:v>
       </x:c>
       <x:c r="F77" s="18" t="str">
-        <x:v>【连续第6期出现】CA产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
+        <x:v>【连续第7期出现】CA产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
       </x:c>
       <x:c r="G77" s="18" t="str">
         <x:v>将事实、备选方案、影响、建议和所需授权统一提交决策人。</x:v>
@@ -3775,7 +3775,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K77" s="10" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L77" s="10" t="str"/>
       <x:c r="M77" s="21" t="str">
@@ -3800,7 +3800,7 @@
         <x:v>决策事项14天内到期</x:v>
       </x:c>
       <x:c r="F78" s="18" t="str">
-        <x:v>【连续第6期出现】电子文档产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
+        <x:v>【连续第7期出现】电子文档产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
       </x:c>
       <x:c r="G78" s="18" t="str">
         <x:v>将事实、备选方案、影响、建议和所需授权统一提交决策人。</x:v>
@@ -3815,7 +3815,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K78" s="10" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L78" s="10" t="str"/>
       <x:c r="M78" s="21" t="str">
@@ -3840,7 +3840,7 @@
         <x:v>决策事项14天内到期</x:v>
       </x:c>
       <x:c r="F79" s="18" t="str">
-        <x:v>【连续第6期出现】BI报表产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
+        <x:v>【连续第7期出现】BI报表产品POC选型决策截止日为2026-09-30，当前状态为待决策。</x:v>
       </x:c>
       <x:c r="G79" s="18" t="str">
         <x:v>将事实、备选方案、影响、建议和所需授权统一提交决策人。</x:v>
@@ -3855,7 +3855,7 @@
         <x:v>46290</x:v>
       </x:c>
       <x:c r="K79" s="10" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L79" s="10" t="str"/>
       <x:c r="M79" s="21" t="str">
@@ -5241,7 +5241,7 @@
         <x:v>运行ID</x:v>
       </x:c>
       <x:c r="B7" s="18" t="str">
-        <x:v>AGENT-20260925-090621</x:v>
+        <x:v>AGENT-20260925-102612</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
